--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="page3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="page4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="page5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="page6" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -76,6 +77,29 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -85,7 +109,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -277,11 +301,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -355,6 +393,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3026,7 +3086,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20.1" customHeight="1" s="11">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -3162,8 +3221,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10" ht="20.1" customHeight="1" s="11">
       <c r="A10" s="16" t="inlineStr">
         <is>
@@ -3338,7 +3395,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="20.1" customHeight="1" s="11">
       <c r="A18" s="16" t="inlineStr">
         <is>
@@ -3850,7 +3906,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="20.1" customHeight="1" s="11">
       <c r="A32" s="27" t="inlineStr">
         <is>
@@ -3858,7 +3913,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="20.1" customHeight="1" s="11">
       <c r="A34" s="16" t="inlineStr">
         <is>
@@ -4088,8 +4142,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="20.1" customHeight="1" s="11">
       <c r="A48" s="16" t="inlineStr">
         <is>
@@ -4319,8 +4371,6 @@
         </is>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62" ht="20.1" customHeight="1" s="11">
       <c r="A62" s="16" t="inlineStr">
         <is>
@@ -4550,8 +4600,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76" ht="20.1" customHeight="1" s="11">
       <c r="A76" s="16" t="inlineStr">
         <is>
@@ -4601,7 +4649,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84" ht="15.95" customHeight="1" s="11">
       <c r="A84" s="12" t="inlineStr">
         <is>
@@ -4660,7 +4707,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20.1" customHeight="1" s="11">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -4828,8 +4874,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="20.1" customHeight="1" s="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -4976,7 +5020,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="20.1" customHeight="1" s="11">
       <c r="A20" s="16" t="inlineStr">
         <is>
@@ -5323,7 +5366,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="20.1" customHeight="1" s="11">
       <c r="A34" s="16" t="inlineStr">
         <is>
@@ -5720,7 +5762,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56" ht="20.1" customHeight="1" s="11">
       <c r="A56" s="27" t="inlineStr">
         <is>
@@ -5728,7 +5769,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58" ht="20.1" customHeight="1" s="11">
       <c r="A58" s="16" t="inlineStr">
         <is>
@@ -5796,8 +5836,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65"/>
     <row r="66" ht="20.1" customHeight="1" s="11">
       <c r="A66" s="16" t="inlineStr">
         <is>
@@ -5919,8 +5957,6 @@
         </is>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73"/>
     <row r="74" ht="20.1" customHeight="1" s="11">
       <c r="A74" s="16" t="inlineStr">
         <is>
@@ -6016,7 +6052,6 @@
       <c r="H79" s="29" t="n"/>
       <c r="I79" s="30" t="n"/>
     </row>
-    <row r="80"/>
     <row r="81" ht="20.1" customHeight="1" s="11">
       <c r="A81" s="16" t="inlineStr">
         <is>
@@ -6059,7 +6094,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88" ht="15.95" customHeight="1" s="11">
       <c r="A88" s="12" t="inlineStr">
         <is>
@@ -8379,4 +8413,1402 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="11" min="1" max="1"/>
+    <col width="14" customWidth="1" style="11" min="2" max="2"/>
+    <col width="12" customWidth="1" style="11" min="3" max="3"/>
+    <col width="14" customWidth="1" style="11" min="4" max="4"/>
+    <col width="42" customWidth="1" style="11" min="5" max="5"/>
+    <col width="30" customWidth="1" style="11" min="6" max="6"/>
+    <col width="10" customWidth="1" style="11" min="7" max="7"/>
+    <col width="10" customWidth="1" style="11" min="8" max="8"/>
+    <col width="10" customWidth="1" style="11" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="11">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>民生基础需求 · 市民反映（page6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="11">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>表A 5 类问题明细（PPT 主体用·城市社区口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="11">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>问题类</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>占板块%</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>涉及社区</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>具体说明（主要为…）</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>聚集社区</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" s="11">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>噪声</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>1,791</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>32.6</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>主要为施工噪声、商业噪声、生活噪声、油烟光污染等扰民问题</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>万达、建设、港务以及岳湾路、大学路</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" s="11">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>停车</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>主要为停车场收费、私设停车位、机动车乱停放等问题</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>万达、港务、张家湾以及岳湾路、宝联</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" s="11">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>1,303</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>主要为老旧小区改造、房屋质量、防水渗漏等住房条件问题</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>建设、港务、万达以及伍临路、枫香树</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" s="11">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>出行</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="inlineStr">
+        <is>
+          <t>主要为道路通行、公交线路、道路设施等出行问题</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>万达、花艳、张家湾以及大学路、建设</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="11">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>物业</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>1,008</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>主要为小区停车、垃圾清运、小区绿化、公共服务配套等物业管理问题</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>港务、万达、伍临路以及建设、张家湾</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="11">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>表B 五类归并总表（城市社区口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="11">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>五类</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>占板块%</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>涉及社区数</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>归并自（原 11 类·件数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="11">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>噪声</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>1,791</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>32.6</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>噪声治理 1,401 + 施工管理 178 + 街面秩序 212</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="11">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>停车</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>停车设施 814</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="11">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>1,303</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>住房 839 + 城市更新 464</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="11">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>出行</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>交通设施 517 + 市政管网 69</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="11">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>物业</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>1,008</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>物业管理 445 + 环境治理 427 + 公服设施 136</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="11">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>5,502</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>总账闭合</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="11">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>注：本表城市社区口径 5,502 条（实测）；行政村 1,865 条单列（见表D）——城市 5,502 + 村 1,865 = 7,367（命中口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="11">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>表C 投诉集中社区 TOP10（城市社区口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="11">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>投诉条数</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>问题占比%</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>严重度</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>主要问题（五类归并）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="11">
+      <c r="A24" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>万达社区</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>8.14</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>噪声 169、停车 83、住宅 75、出行 51、物业 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="11">
+      <c r="A25" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>港务社区</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>噪声 100、停车 48、住宅 79、物业 92</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="11">
+      <c r="A26" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>建设社区</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>噪声 149、停车 23、住宅 88、物业 38</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="11">
+      <c r="A27" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>岳湾路社区</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>较严重</t>
+        </is>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>噪声 89、停车 38、住宅 35、物业 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" s="11">
+      <c r="A28" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>伍临路社区</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>较严重</t>
+        </is>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>噪声 66、住宅 68、物业 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" s="11">
+      <c r="A29" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>大学路社区</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>较严重</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>噪声 72、停车 25、住宅 30、出行 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" s="11">
+      <c r="A30" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>张家湾社区</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>噪声 44、停车 41、物业 35</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" s="11">
+      <c r="A31" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>宝联社区</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>噪声 43、停车 31、住宅 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" s="11">
+      <c r="A32" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>枫香树社区</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>住宅 38、噪声 23、停车 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" s="11">
+      <c r="A33" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>营盘路社区</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>住宅 34、噪声 32、物业 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1" s="11">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>严重度分档：占板块 ≥5% 严重 / 3~5% 较严重 / &lt;3% 一般（占比分母 = 城市社区 5,502）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="11">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>表D 行政村民生诉求排行（17 村 · 1,865 条）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" s="11">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>诉求数</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="inlineStr">
+        <is>
+          <t>占比%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="11">
+      <c r="A38" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>共勤村</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="11">
+      <c r="A39" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>旭光村</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="11">
+      <c r="A40" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>汉宜村</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="11">
+      <c r="A41" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>火光村</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="11">
+      <c r="A42" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>共和村</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="11">
+      <c r="A43" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>合益村</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="11">
+      <c r="A44" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>共联村</t>
+        </is>
+      </c>
+      <c r="C44" s="35" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="11">
+      <c r="A45" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>土门村</t>
+        </is>
+      </c>
+      <c r="C45" s="35" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="11">
+      <c r="A46" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>共同村</t>
+        </is>
+      </c>
+      <c r="C46" s="35" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="11">
+      <c r="A47" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>联丰村</t>
+        </is>
+      </c>
+      <c r="C47" s="35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1" s="11">
+      <c r="A48" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B48" s="34" t="inlineStr">
+        <is>
+          <t>共前村</t>
+        </is>
+      </c>
+      <c r="C48" s="35" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" s="11">
+      <c r="A49" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>共升村</t>
+        </is>
+      </c>
+      <c r="C49" s="35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="11">
+      <c r="A50" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="B50" s="34" t="inlineStr">
+        <is>
+          <t>共强村</t>
+        </is>
+      </c>
+      <c r="C50" s="35" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="11">
+      <c r="A51" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>梅花村</t>
+        </is>
+      </c>
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1" s="11">
+      <c r="A52" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="B52" s="34" t="inlineStr">
+        <is>
+          <t>共谊村</t>
+        </is>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" s="11">
+      <c r="A53" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B53" s="34" t="inlineStr">
+        <is>
+          <t>车站村</t>
+        </is>
+      </c>
+      <c r="C53" s="35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="11">
+      <c r="A54" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>灵宝村</t>
+        </is>
+      </c>
+      <c r="C54" s="35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1" s="11">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t>村口径 = 村内点图层（board=民生基础需求）1,865 条·17 村·占比分母 1,865；18 村中仅 17 村有民生诉求</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" s="11">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>表E 双轨对照（page5 体检结果 ↔ 本页市民反映）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1" s="11">
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>主题</t>
+        </is>
+      </c>
+      <c r="B58" s="33" t="inlineStr">
+        <is>
+          <t>体检发现（page5）</t>
+        </is>
+      </c>
+      <c r="C58" s="33" t="inlineStr">
+        <is>
+          <t>市民反映（本页）</t>
+        </is>
+      </c>
+      <c r="D58" s="33" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1" s="11">
+      <c r="A59" s="35" t="inlineStr">
+        <is>
+          <t>停车</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>泊位 140 处/充电桩 84 处/电动车 50 个</t>
+        </is>
+      </c>
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>814 条（收费/私设/乱停放）</t>
+        </is>
+      </c>
+      <c r="D59" s="38" t="n"/>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1" s="11">
+      <c r="A60" s="35" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+      <c r="B60" s="34" t="inlineStr">
+        <is>
+          <t>非成套 31 处/适老化 39 处</t>
+        </is>
+      </c>
+      <c r="C60" s="34" t="inlineStr">
+        <is>
+          <t>1,303 条（老旧改造/质量/防水）</t>
+        </is>
+      </c>
+      <c r="D60" s="38" t="n"/>
+      <c r="E60" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1" s="11">
+      <c r="A61" s="35" t="inlineStr">
+        <is>
+          <t>物业</t>
+        </is>
+      </c>
+      <c r="B61" s="34" t="inlineStr">
+        <is>
+          <t>未物业小区 273 个/乱停放 5 处</t>
+        </is>
+      </c>
+      <c r="C61" s="34" t="inlineStr">
+        <is>
+          <t>1,008 条</t>
+        </is>
+      </c>
+      <c r="D61" s="38" t="n"/>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1" s="11">
+      <c r="A62" s="35" t="inlineStr">
+        <is>
+          <t>公服设施</t>
+        </is>
+      </c>
+      <c r="B62" s="34" t="inlineStr">
+        <is>
+          <t>养老/托育/幼儿园/学位 8 项缺口</t>
+        </is>
+      </c>
+      <c r="C62" s="34" t="inlineStr">
+        <is>
+          <t>136 条（诉求较少）</t>
+        </is>
+      </c>
+      <c r="D62" s="38" t="n"/>
+      <c r="E62" s="34" t="inlineStr">
+        <is>
+          <t>◐ 体检独证（学位/养老缺口市民直接诉求少·多为规划配置问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1" s="11">
+      <c r="A63" s="35" t="inlineStr">
+        <is>
+          <t>出行</t>
+        </is>
+      </c>
+      <c r="B63" s="34" t="inlineStr">
+        <is>
+          <t>不达标步行道 2.09 千米</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>586 条（道路通行/公交）</t>
+        </is>
+      </c>
+      <c r="D63" s="38" t="n"/>
+      <c r="E63" s="34" t="inlineStr">
+        <is>
+          <t>✓ 相关印证</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1" s="11">
+      <c r="A64" s="35" t="inlineStr">
+        <is>
+          <t>（体检无对应）</t>
+        </is>
+      </c>
+      <c r="B64" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
+          <t>噪声 1,791 条</t>
+        </is>
+      </c>
+      <c r="D64" s="38" t="n"/>
+      <c r="E64" s="34" t="inlineStr">
+        <is>
+          <t>◑ 市民独证（噪声是体检盲区·民生诉求最大类）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1" s="11">
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>表F 口径详注</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1" s="11">
+      <c r="A68" s="37" t="inlineStr">
+        <is>
+          <t>① 承接 page2 线二：83.3% 属于底线与民生（47,693 件）中民生基础 = 42,871 件（三层定稿·74.9%）；本页主体用命中口径（城市 5,502 + 村 1,865 = 7,367）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1" s="11">
+      <c r="A69" s="37" t="inlineStr">
+        <is>
+          <t>② 五类归并（用户定稿）：噪声=噪声治理+施工管理+街面秩序；停车=停车设施；住宅=住房+城市更新；出行=交通设施+市政管网；物业=物业管理+环境治理+公服设施</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1" s="11">
+      <c r="A70" s="37" t="inlineStr">
+        <is>
+          <t>③ 社区口径：城市社区 148（CSV 实测）+ 行政村 17（18 村中 17 村有民生诉求）= 165；与 page4 的“126 城市社区+18 村”同法拆分</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1" s="11">
+      <c r="A71" s="37" t="inlineStr">
+        <is>
+          <t>④ 占比分母：城市社区 5,502（表A/C）·村 1,865（表D）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1" s="11">
+      <c r="A72" s="37" t="inlineStr">
+        <is>
+          <t>⑤ 数据审计：旧素材 7,340/165 含村口径已按实测修正（城市 5,502 + 村 1,865 = 7,367·与旧 7,340 差 27 条为源数据漂移）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1" s="11">
+      <c r="A73" s="37" t="inlineStr">
+        <is>
+          <t>⑥ 数据源红线：中转站真实数据·sim 禁入</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1" s="11">
+      <c r="A75" s="37" t="inlineStr">
+        <is>
+          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v2）· 制作：Codex · 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A72:I72"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -8509,7 +8509,7 @@
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>万达、建设、港务以及岳湾路、大学路</t>
+          <t>万达、建设、港务、岳湾路、大学路</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>万达、港务、张家湾以及岳湾路、宝联</t>
+          <t>万达、港务、张家湾、岳湾路、宝联</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>建设、港务、万达以及伍临路、枫香树</t>
+          <t>建设、港务、万达、伍临路、枫香树</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>万达、花艳、张家湾以及大学路、建设</t>
+          <t>万达、花艳、张家湾、大学路、建设</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>港务、万达、伍临路以及建设、张家湾</t>
+          <t>港务、万达、伍临路、建设、张家湾</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A34:I34"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A68:I68"/>
@@ -9804,7 +9804,7 @@
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A72:I72"/>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -319,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -415,6 +415,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8445,7 +8447,7 @@
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>表A 5 类问题明细（PPT 主体用·城市社区口径）</t>
+          <t>表A 5 类问题明细（PPT 主体用·含村口径）</t>
         </is>
       </c>
     </row>
@@ -8489,17 +8491,17 @@
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>1,791</t>
+          <t>2,425</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>122 城市社区 + 16 村</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -8509,7 +8511,7 @@
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>万达、建设、港务、岳湾路、大学路</t>
+          <t>万达、建设、港务、岳湾路、大学路 以及共勤村、旭光村、汉宜村</t>
         </is>
       </c>
     </row>
@@ -8521,17 +8523,17 @@
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>112 城市社区 + 16 村</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -8541,7 +8543,7 @@
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>万达、港务、张家湾、岳湾路、宝联</t>
+          <t>万达、港务、张家湾、岳湾路、宝联 以及共勤村、旭光村、汉宜村</t>
         </is>
       </c>
     </row>
@@ -8553,17 +8555,17 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>1,303</t>
+          <t>1,597</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>119 城市社区 + 16 村</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -8573,7 +8575,7 @@
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>建设、港务、万达、伍临路、枫香树</t>
+          <t>建设、港务、万达、伍临路、枫香树 以及共勤村、汉宜村、火光村</t>
         </is>
       </c>
     </row>
@@ -8585,17 +8587,17 @@
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>813</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>107 城市社区 + 15 村</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -8605,7 +8607,7 @@
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>万达、花艳、张家湾、大学路、建设</t>
+          <t>万达、花艳、张家湾、大学路、建设 以及共和村、旭光村、共勤村</t>
         </is>
       </c>
     </row>
@@ -8617,17 +8619,17 @@
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>1,008</t>
+          <t>1,372</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>121 城市社区 + 16 村</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -8637,14 +8639,14 @@
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>港务、万达、伍临路、建设、张家湾</t>
+          <t>港务、万达、伍临路、建设、张家湾 以及共勤村、旭光村、汉宜村</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" s="11">
       <c r="A12" s="32" t="inlineStr">
         <is>
-          <t>表B 五类归并总表（城市社区口径）</t>
+          <t>表B 五类归并总表（含村口径·城市社区 + 行政村）</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8658,7 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>件数</t>
+          <t>件数（含村）</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
@@ -8666,12 +8668,17 @@
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>涉及社区数</t>
+          <t>城市社区</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>归并自（原 11 类·件数）</t>
+          <t>行政村</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>归并自（原 11 类）</t>
         </is>
       </c>
     </row>
@@ -8683,22 +8690,27 @@
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>1,791</t>
+          <t>2,425</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1,791（122 社区）</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>噪声治理 1,401 + 施工管理 178 + 街面秩序 212</t>
+          <t>634（16 村）</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t>噪声治理+施工管理+街面秩序</t>
         </is>
       </c>
     </row>
@@ -8710,22 +8722,27 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>814（112 社区）</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>停车设施 814</t>
+          <t>346（16 村）</t>
+        </is>
+      </c>
+      <c r="F15" s="39" t="inlineStr">
+        <is>
+          <t>停车设施</t>
         </is>
       </c>
     </row>
@@ -8737,22 +8754,27 @@
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>1,303</t>
+          <t>1,597</t>
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1,303（119 社区）</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>住房 839 + 城市更新 464</t>
+          <t>294（16 村）</t>
+        </is>
+      </c>
+      <c r="F16" s="39" t="inlineStr">
+        <is>
+          <t>住房+城市更新</t>
         </is>
       </c>
     </row>
@@ -8764,22 +8786,27 @@
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>813</t>
         </is>
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>586（107 社区）</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>交通设施 517 + 市政管网 69</t>
+          <t>227（15 村）</t>
+        </is>
+      </c>
+      <c r="F17" s="39" t="inlineStr">
+        <is>
+          <t>交通设施+市政管网</t>
         </is>
       </c>
     </row>
@@ -8791,22 +8818,27 @@
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>1,008</t>
+          <t>1,372</t>
         </is>
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1,008（121 社区）</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>物业管理 445 + 环境治理 427 + 公服设施 136</t>
+          <t>364（16 村）</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>物业管理+环境治理+公服设施</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8850,7 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>5,502</t>
+          <t>7,367</t>
         </is>
       </c>
       <c r="C19" s="33" t="inlineStr">
@@ -8828,10 +8860,15 @@
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>5,502（148 社区）</t>
         </is>
       </c>
       <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>1,865（17 村）</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>总账闭合</t>
         </is>
@@ -8840,7 +8877,7 @@
     <row r="20" ht="30" customHeight="1" s="11">
       <c r="A20" s="37" t="inlineStr">
         <is>
-          <t>注：本表城市社区口径 5,502 条（实测）；行政村 1,865 条单列（见表D）——城市 5,502 + 村 1,865 = 7,367（命中口径）</t>
+          <t>注：五类明细含村（城市 5,502 + 村 1,865 = 7,367·命中口径）；行政村 17 村 1,865 条单列（见表D）</t>
         </is>
       </c>
     </row>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -4689,1445 +4689,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
-    <col width="16" customWidth="1" style="11" min="2" max="2"/>
-    <col width="28" customWidth="1" style="11" min="3" max="3"/>
-    <col width="16" customWidth="1" style="11" min="4" max="4"/>
+    <col width="14" customWidth="1" style="11" min="2" max="2"/>
+    <col width="12" customWidth="1" style="11" min="3" max="3"/>
+    <col width="14" customWidth="1" style="11" min="4" max="4"/>
     <col width="42" customWidth="1" style="11" min="5" max="5"/>
     <col width="28" customWidth="1" style="11" min="6" max="6"/>
-    <col width="10" customWidth="1" style="11" min="7" max="8"/>
-    <col width="30" customWidth="1" style="11" min="9" max="9"/>
+    <col width="10" customWidth="1" style="11" min="7" max="7"/>
+    <col width="10" customWidth="1" style="11" min="8" max="8"/>
+    <col width="10" customWidth="1" style="11" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" s="11">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="11">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>安全韧性问题 · 市民反映（page4）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" s="11">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>表A 4 类问题明细（PPT 主体用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21.95" customHeight="1" s="11">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="3" ht="20" customHeight="1" s="11">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>表A 4 类问题明细（ok 可落图·社区+村）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="11">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>问题类</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>投诉条数</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>涉及社区</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>占 ok%</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>社区/村</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>具体说明</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>聚集社区</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" s="11">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>管网安全</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>50.3%</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>主要为路灯、井盖、化粪池、管线等设施损坏、失修等问题</t>
-        </is>
-      </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>港务、汉宜村、建设、万达、共勤村</t>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>762 + 12</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>主要为路灯、井盖、化粪池、管线等设施损坏失修</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>港务、东星、汕头路、花艳、宝联</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" s="11">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>出行安全</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>37.6%</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E6" s="28" t="inlineStr">
-        <is>
-          <t>主要为交通信号灯、人行道、车行道等设施破损、道路坑洼等问题</t>
-        </is>
-      </c>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>汉宜村、大学路、旭光村、万达、港务</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>538 + 18</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>主要为道路破损、桥梁损坏、交通设施故障</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>港务、东星、大学路、张家湾、宝联</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" s="11">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>消防安全</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>11.0%</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E7" s="28" t="inlineStr">
-        <is>
-          <t>主要为消防通道占用、消防器材缺失损坏等问题（与 page3 体检“楼道消防隐患 240 栋”双轨呼应）</t>
-        </is>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>港务、建设、汉宜村、旭光村、体育场路</t>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>171 + 8</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>主要为消防通道占用、器材缺失</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>港务、艾家嘴、魏家湾、汕头路、宝联</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" s="11">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>环境安全</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
-        <is>
-          <t>主要为山体滑坡、堡坎坍塌等地质灾害风险问题（数量少但风险性质最重）</t>
-        </is>
-      </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>体育场路、共前村、大学路、朝阳路、共联村</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20.1" customHeight="1" s="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>表B 各类问题规模总表（PPT 主体用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21.95" customHeight="1" s="11">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>20 + 0</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="inlineStr">
+        <is>
+          <t>主要为山体滑坡、堡坎坍塌（风险最重）</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>体育场路、黄金卡、福久源、冯家湾、梅子溪</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="11">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>表B 规模总表（有坐标分级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="11">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>问题类</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>投诉条数</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>涉及社区（村）</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>占板块%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21.95" customHeight="1" s="11">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>ok 社区+村</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>region 区级</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>有坐标合计</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>占 ok%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="11">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>管网安全</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21.95" customHeight="1" s="11">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>1,325</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="11">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>出行安全</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>37.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21.95" customHeight="1" s="11">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="11">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>消防安全</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="11">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>环境安全</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="11">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>1,529</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>2,657</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="11">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>口径链：全量 5,005 → 有坐标 2,657（ok 1,713+region 944）→ ok 可落图 1,529</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="11">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>表C 社区 TOP8（ok 点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="11">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>诉求数</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>占 ok%</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>主要问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="11">
+      <c r="A20" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>港务社区</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="21.95" customHeight="1" s="11">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>环境安全</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21.95" customHeight="1" s="11">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>1,376</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>144（126 社区+18 村）</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="11">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>口径链：4,800（全量·三层定稿）→ 4,601（其中投诉）→ 1,376（投诉中命中中心城区体检对象·城市社区 1,063+18 村 313）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20.1" customHeight="1" s="11">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>表C 问题较严重社区 TOP10（城市社区口径）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21.95" customHeight="1" s="11">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>投诉条数</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>问题占比%</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>严重度</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>主要问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="21.95" customHeight="1" s="11">
-      <c r="A22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t>港务社区</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="F22" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 53、出行安全 17、消防安全 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="21.95" customHeight="1" s="11">
-      <c r="A23" s="13" t="n">
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>管网 98、出行安全 46、消防 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="11">
+      <c r="A21" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>建设社区</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>东星社区</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>管网 50、出行安全 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="11">
+      <c r="A22" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>宝联社区</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>较严重</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 27、出行安全 12、消防安全 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="21.95" customHeight="1" s="11">
-      <c r="A24" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>万达社区</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>较严重</t>
-        </is>
-      </c>
-      <c r="F24" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 26、出行安全 21</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="21.95" customHeight="1" s="11">
-      <c r="A25" s="13" t="n">
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>管网 23、出行安全 18、消防 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="11">
+      <c r="A23" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>汕头路社区</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>管网 26、消防 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="11">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>花艳社区</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="inlineStr">
+        <is>
+          <t>管网 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="11">
+      <c r="A25" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>张家湾社区</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>出行安全 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="11">
+      <c r="A26" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>大学路社区</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>较严重</t>
-        </is>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
-        <is>
-          <t>出行安全 24、管网安全 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="21.95" customHeight="1" s="11">
-      <c r="A26" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="28" t="inlineStr">
-        <is>
-          <t>体育场路社区</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F26" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 13、出行安全 7、消防安全 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="21.95" customHeight="1" s="11">
-      <c r="A27" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" s="28" t="inlineStr">
-        <is>
-          <t>宝联社区</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 18、出行安全 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="21.95" customHeight="1" s="11">
-      <c r="A28" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B28" s="28" t="inlineStr">
-        <is>
-          <t>张家湾社区</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F28" s="28" t="inlineStr">
-        <is>
-          <t>出行安全 13、管网安全 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="21.95" customHeight="1" s="11">
-      <c r="A29" s="13" t="n">
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="inlineStr">
+        <is>
+          <t>出行安全 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="11">
+      <c r="A27" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="28" t="inlineStr">
-        <is>
-          <t>朝阳路社区</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F29" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 12、出行安全 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21.95" customHeight="1" s="11">
-      <c r="A30" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>胜利四路社区</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F30" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 9、出行安全 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="21.95" customHeight="1" s="11">
-      <c r="A31" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B31" s="28" t="inlineStr">
-        <is>
-          <t>伍临路社区</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F31" s="28" t="inlineStr">
-        <is>
-          <t>管网安全 10、出行安全 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.95" customHeight="1" s="11">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>占比分母 = 城市社区口径 1,063 条（非 1,376·18 村单列·见下表C-2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20.1" customHeight="1" s="11">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>表C-2 行政村安全韧性诉求排行（18 村·村内点图层）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="21.95" customHeight="1" s="11">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>村</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>诉求数</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>占比%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1" s="11">
-      <c r="A36" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="28" t="inlineStr">
-        <is>
-          <t>汉宜村</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" s="11">
-      <c r="A37" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>旭光村</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1" s="11">
-      <c r="A38" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>共勤村</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1" s="11">
-      <c r="A39" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B39" s="28" t="inlineStr">
-        <is>
-          <t>共和村</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1" s="11">
-      <c r="A40" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B40" s="28" t="inlineStr">
-        <is>
-          <t>火光村</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1" s="11">
-      <c r="A41" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B41" s="28" t="inlineStr">
-        <is>
-          <t>共联村</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1" s="11">
-      <c r="A42" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" s="28" t="inlineStr">
-        <is>
-          <t>土门村</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" s="11">
-      <c r="A43" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B43" s="28" t="inlineStr">
-        <is>
-          <t>合益村</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1" s="11">
-      <c r="A44" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B44" s="28" t="inlineStr">
-        <is>
-          <t>共谊村</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>魏家湾社区</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="18" customHeight="1" s="11">
-      <c r="A45" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B45" s="28" t="inlineStr">
-        <is>
-          <t>车站村</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1" s="11">
-      <c r="A46" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B46" s="28" t="inlineStr">
-        <is>
-          <t>共同村</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1" s="11">
-      <c r="A47" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B47" s="28" t="inlineStr">
-        <is>
-          <t>共升村</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1" s="11">
-      <c r="A48" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="28" t="inlineStr">
-        <is>
-          <t>联丰村</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" s="11">
-      <c r="A49" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B49" s="28" t="inlineStr">
-        <is>
-          <t>共前村</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1" s="11">
-      <c r="A50" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B50" s="28" t="inlineStr">
-        <is>
-          <t>灵宝村</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" s="11">
-      <c r="A51" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B51" s="28" t="inlineStr">
-        <is>
-          <t>共强村</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1" s="11">
-      <c r="A52" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B52" s="28" t="inlineStr">
-        <is>
-          <t>梅花村</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" s="11">
-      <c r="A53" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B53" s="28" t="inlineStr">
-        <is>
-          <t>前坪村</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1" s="11">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>村口径 = 村内点图层（12345_村内点.geojson·board=安全韧性底线）315 条·18 村·占比分母 315；与城市社区 1,063 合计 1,378（口径链 1,376 为投诉口径·差 2 条源数据差异）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20.1" customHeight="1" s="11">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>—— 备查详表（PPT 主体不展示 · 讲稿/答疑/口径溯源用）——</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20.1" customHeight="1" s="11">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>表D 每类聚集社区（村）TOP5</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="21.95" customHeight="1" s="11">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>问题类</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>聚集 TOP5（含村）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="21.95" customHeight="1" s="11">
-      <c r="A60" s="28" t="inlineStr">
-        <is>
-          <t>管网安全</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="inlineStr">
-        <is>
-          <t>港务社区、汉宜村、建设社区、万达社区、共勤村</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="21.95" customHeight="1" s="11">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>出行安全</t>
-        </is>
-      </c>
-      <c r="B61" s="28" t="inlineStr">
-        <is>
-          <t>汉宜村、大学路社区、旭光村、万达社区、港务社区</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="21.95" customHeight="1" s="11">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>消防安全</t>
-        </is>
-      </c>
-      <c r="B62" s="28" t="inlineStr">
-        <is>
-          <t>港务社区、建设社区、汉宜村、旭光村、体育场路社区</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="21.95" customHeight="1" s="11">
-      <c r="A63" s="28" t="inlineStr">
-        <is>
-          <t>环境安全</t>
-        </is>
-      </c>
-      <c r="B63" s="28" t="inlineStr">
-        <is>
-          <t>体育场路社区、共前村、大学路社区、朝阳路社区、共联村</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20.1" customHeight="1" s="11">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>表E 双轨对照（page3 体检结果 ↔ 本页市民反映）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="21.95" customHeight="1" s="11">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>主题</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>体检发现</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>市民反映</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45.95" customHeight="1" s="11">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>管网安全</t>
-        </is>
-      </c>
-      <c r="B68" s="28" t="inlineStr">
-        <is>
-          <t>燃气 6 栋 + 管线 186 栋</t>
-        </is>
-      </c>
-      <c r="C68" s="28" t="inlineStr">
-        <is>
-          <t>692 条（路灯/井盖/化粪池/管线）</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="28" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦（可信度最高·优先治理）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45.95" customHeight="1" s="11">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>消防安全</t>
-        </is>
-      </c>
-      <c r="B69" s="28" t="inlineStr">
-        <is>
-          <t>楼道隐患 240 栋</t>
-        </is>
-      </c>
-      <c r="C69" s="28" t="inlineStr">
-        <is>
-          <t>151 条（通道被占/器材缺失）</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="28" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦（消防通道占用双向印证）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45.95" customHeight="1" s="11">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>房屋安全</t>
-        </is>
-      </c>
-      <c r="B70" s="28" t="inlineStr">
-        <is>
-          <t>结构 42 栋 + 围护 454 栋</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="inlineStr">
-        <is>
-          <t>结构隐患市民几乎不诉</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="28" t="inlineStr">
-        <is>
-          <t>◐ 体检独证（结构隐患需专业鉴定方能识别·围护投诉归入民生类反映）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="45.95" customHeight="1" s="11">
-      <c r="A71" s="13" t="inlineStr">
-        <is>
-          <t>出行安全</t>
-        </is>
-      </c>
-      <c r="B71" s="28" t="inlineStr">
-        <is>
-          <t>（体检未覆盖·盲区）</t>
-        </is>
-      </c>
-      <c r="C71" s="28" t="inlineStr">
-        <is>
-          <t>517 条（信号灯/路面/人行道）</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="28" t="inlineStr">
-        <is>
-          <t>◑ 市民独证（12345 补体检覆盖不足）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20.1" customHeight="1" s="11">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>表F 主要小类件数（备查·全量口径）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="21.95" customHeight="1" s="11">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>问题类</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>主要小类（全量口径件数·与命中口径不同分母·不可混算）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1" s="11">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>管网安全</t>
-        </is>
-      </c>
-      <c r="B76" s="28" t="inlineStr">
-        <is>
-          <t>路灯破损 782、化粪池满溢 452、井盖破损缺失移位 359、自来水管破裂 335、污水井盖 297、高空线缆 243、消防设施漏水破损 240（注：此小类实为消防类·旧归属市政·仅标注不重复计）、电线杆 191、排水设施堵塞 184</t>
-        </is>
-      </c>
-      <c r="C76" s="29" t="n"/>
-      <c r="D76" s="29" t="n"/>
-      <c r="E76" s="29" t="n"/>
-      <c r="F76" s="29" t="n"/>
-      <c r="G76" s="29" t="n"/>
-      <c r="H76" s="29" t="n"/>
-      <c r="I76" s="30" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1" s="11">
-      <c r="A77" s="13" t="inlineStr">
-        <is>
-          <t>出行安全</t>
-        </is>
-      </c>
-      <c r="B77" s="28" t="inlineStr">
-        <is>
-          <t>交通信号灯破损 919、人行道破损 451、车行道破损 186、侧石止车石破损 225、路面塌陷 181、公交站台设施破损 139、交通护栏破损 147、道路积水 136</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="n"/>
-      <c r="D77" s="29" t="n"/>
-      <c r="E77" s="29" t="n"/>
-      <c r="F77" s="29" t="n"/>
-      <c r="G77" s="29" t="n"/>
-      <c r="H77" s="29" t="n"/>
-      <c r="I77" s="30" t="n"/>
-    </row>
-    <row r="78" ht="30" customHeight="1" s="11">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>消防安全</t>
-        </is>
-      </c>
-      <c r="B78" s="28" t="inlineStr">
-        <is>
-          <t>占用消防通道 442、消防器材问题 84、消防车道占用堵塞 83、通道应急照明疏散标志 35、灭火器未配备损坏 32</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="n"/>
-      <c r="D78" s="29" t="n"/>
-      <c r="E78" s="29" t="n"/>
-      <c r="F78" s="29" t="n"/>
-      <c r="G78" s="29" t="n"/>
-      <c r="H78" s="29" t="n"/>
-      <c r="I78" s="30" t="n"/>
-    </row>
-    <row r="79" ht="30" customHeight="1" s="11">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>环境安全</t>
-        </is>
-      </c>
-      <c r="B79" s="28" t="inlineStr">
-        <is>
-          <t>山体滑坡堡坎坍塌 151、堡坎存在安全隐患 49、堡坎渗水 15</t>
-        </is>
-      </c>
-      <c r="C79" s="29" t="n"/>
-      <c r="D79" s="29" t="n"/>
-      <c r="E79" s="29" t="n"/>
-      <c r="F79" s="29" t="n"/>
-      <c r="G79" s="29" t="n"/>
-      <c r="H79" s="29" t="n"/>
-      <c r="I79" s="30" t="n"/>
-    </row>
-    <row r="81" ht="20.1" customHeight="1" s="11">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t>口径详注</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15.95" customHeight="1" s="11">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>① 承接 page2 线二：83.3% 属于底线与民生（47,693 件）中安全韧性 = 4,800 件（三层定稿·投诉+求助）；本页主体用命中口径 1,376 条投诉</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15.95" customHeight="1" s="11">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>② 126 城市社区（174 口径）+ 18 行政村（伍家乡城中村）；表C 为城市社区口径·表C-2 为村口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15.95" customHeight="1" s="11">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>③ 严重度分档：≥5% 严重 / 3~5% 较严重 / &lt;3% 一般（表C 占比分母 = 城市社区 1,063·表C-2 占比分母 = 村 315）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15.95" customHeight="1" s="11">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>④ 主要小类件数为全量口径（如路灯 782）·与命中口径 692 不同分母·不可混算</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15.95" customHeight="1" s="11">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>⑤ 数据源红线：中转站真实数据·sim 禁入</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15.95" customHeight="1" s="11">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v2）· 制作：Codex · 2026-08-13</t>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>消防 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" s="11">
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>行政村（ok）：火光村 14、共升村 10、灵宝村 4、旭光村 3、共勤村 2、联丰村 2、共联村 2、共前村 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1" s="11">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>数据源：12345_治理清洗版+checkup 治理产出（CB-30）· 社区/村/区级分级 · 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A66:I66"/>
+  <mergeCells count="7">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A86:I86"/>
-    <mergeCell ref="B77:I77"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A81:I81"/>
-    <mergeCell ref="B78:I78"/>
-    <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A88:I88"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8423,15 +7605,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="11" min="1" max="1"/>
+    <col width="18" customWidth="1" style="11" min="1" max="1"/>
     <col width="14" customWidth="1" style="11" min="2" max="2"/>
     <col width="12" customWidth="1" style="11" min="3" max="3"/>
     <col width="14" customWidth="1" style="11" min="4" max="4"/>
     <col width="42" customWidth="1" style="11" min="5" max="5"/>
-    <col width="30" customWidth="1" style="11" min="6" max="6"/>
+    <col width="28" customWidth="1" style="11" min="6" max="6"/>
     <col width="10" customWidth="1" style="11" min="7" max="7"/>
     <col width="10" customWidth="1" style="11" min="8" max="8"/>
     <col width="10" customWidth="1" style="11" min="9" max="9"/>
@@ -8447,7 +7629,7 @@
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>表A 5 类问题明细（PPT 主体用·含村口径）</t>
+          <t>表A 5 类问题明细（ok 可落图·社区+村）</t>
         </is>
       </c>
     </row>
@@ -8464,17 +7646,17 @@
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>占板块%</t>
+          <t>占 ok%</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>涉及社区</t>
+          <t>社区/村</t>
         </is>
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
-          <t>具体说明（主要为…）</t>
+          <t>具体说明</t>
         </is>
       </c>
       <c r="F4" s="33" t="inlineStr">
@@ -8491,27 +7673,27 @@
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>2,425</t>
+          <t>2,861</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>122 城市社区 + 16 村</t>
+          <t>2,807 + 54</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
-          <t>主要为施工噪声、商业噪声、生活噪声、油烟光污染等扰民问题</t>
+          <t>主要为施工、商业、生活噪声及油烟光污染</t>
         </is>
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>万达、建设、港务、岳湾路、大学路 以及共勤村、旭光村、汉宜村</t>
+          <t>港务、汕头路、宝联、八一路、伍临路</t>
         </is>
       </c>
     </row>
@@ -8523,27 +7705,27 @@
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,312</t>
         </is>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>112 城市社区 + 16 村</t>
+          <t>1,291 + 21</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
-          <t>主要为停车场收费、私设停车位、机动车乱停放等问题</t>
+          <t>主要为停车收费、私设车位、乱停放</t>
         </is>
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>万达、港务、张家湾、岳湾路、宝联 以及共勤村、旭光村、汉宜村</t>
+          <t>港务、宝联、八一路、张家湾、汕头路</t>
         </is>
       </c>
     </row>
@@ -8555,27 +7737,27 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>1,597</t>
+          <t>1,956</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>119 城市社区 + 16 村</t>
+          <t>1,934 + 22</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
-          <t>主要为老旧小区改造、房屋质量、防水渗漏等住房条件问题</t>
+          <t>主要为老旧改造、房屋质量、防水渗漏</t>
         </is>
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>建设、港务、万达、伍临路、枫香树 以及共勤村、汉宜村、火光村</t>
+          <t>港务、汕头路、伍临路、魏家湾、东星</t>
         </is>
       </c>
     </row>
@@ -8587,27 +7769,27 @@
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>898</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>107 城市社区 + 15 村</t>
+          <t>867 + 31</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
-          <t>主要为道路通行、公交线路、道路设施等出行问题</t>
+          <t>主要为道路通行、公交线路、道路设施</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>万达、花艳、张家湾、大学路、建设 以及共和村、旭光村、共勤村</t>
+          <t>港务、东站路、汕头路、花艳、宝联</t>
         </is>
       </c>
     </row>
@@ -8619,430 +7801,420 @@
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>1,372</t>
+          <t>1,535</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>121 城市社区 + 16 村</t>
+          <t>1,495 + 40</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
-          <t>主要为小区停车、垃圾清运、小区绿化、公共服务配套等物业管理问题</t>
+          <t>主要为小区停车、垃圾、绿化、公服配套</t>
         </is>
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>港务、万达、伍临路、建设、张家湾 以及共勤村、旭光村、汉宜村</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="11">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>表B 五类归并总表（含村口径·城市社区 + 行政村）</t>
+          <t>港务、汕头路、宝联、东星、张家湾</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>表B 规模总表（有坐标分级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="11">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>问题类</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>ok 社区+村</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>region 区级</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>有坐标合计</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>占 ok%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" s="11">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>五类</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>件数（含村）</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>占板块%</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>城市社区</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t>行政村</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>归并自（原 11 类）</t>
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>噪声</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>2,861</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>1,674</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>4,535</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>33.4</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" s="11">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>噪声</t>
+          <t>停车</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>2,425</t>
+          <t>1,312</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>1,087</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>1,791（122 社区）</t>
-        </is>
-      </c>
-      <c r="E14" s="34" t="inlineStr">
-        <is>
-          <t>634（16 村）</t>
-        </is>
-      </c>
-      <c r="F14" s="39" t="inlineStr">
-        <is>
-          <t>噪声治理+施工管理+街面秩序</t>
+          <t>2,399</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>15.3</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" s="11">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>停车</t>
+          <t>住宅</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,956</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>1,334</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>814（112 社区）</t>
-        </is>
-      </c>
-      <c r="E15" s="34" t="inlineStr">
-        <is>
-          <t>346（16 村）</t>
-        </is>
-      </c>
-      <c r="F15" s="39" t="inlineStr">
-        <is>
-          <t>停车设施</t>
+          <t>3,290</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>22.8</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="11">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>住宅</t>
+          <t>出行</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>1,597</t>
+          <t>898</t>
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>664</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>1,303（119 社区）</t>
-        </is>
-      </c>
-      <c r="E16" s="34" t="inlineStr">
-        <is>
-          <t>294（16 村）</t>
-        </is>
-      </c>
-      <c r="F16" s="39" t="inlineStr">
-        <is>
-          <t>住房+城市更新</t>
+          <t>1,562</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>10.5</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" s="11">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>出行</t>
+          <t>物业</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1,535</t>
         </is>
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1,220</t>
         </is>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>586（107 社区）</t>
-        </is>
-      </c>
-      <c r="E17" s="34" t="inlineStr">
-        <is>
-          <t>227（15 村）</t>
-        </is>
-      </c>
-      <c r="F17" s="39" t="inlineStr">
-        <is>
-          <t>交通设施+市政管网</t>
+          <t>2,755</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>17.9</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" s="11">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>物业</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>1,372</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="D18" s="35" t="inlineStr">
-        <is>
-          <t>1,008（121 社区）</t>
-        </is>
-      </c>
-      <c r="E18" s="34" t="inlineStr">
-        <is>
-          <t>364（16 村）</t>
-        </is>
-      </c>
-      <c r="F18" s="39" t="inlineStr">
-        <is>
-          <t>物业管理+环境治理+公服设施</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="11">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>7,367</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>8,562</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>5,979</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>14,541</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>5,502（148 社区）</t>
-        </is>
-      </c>
-      <c r="E19" s="36" t="inlineStr">
-        <is>
-          <t>1,865（17 村）</t>
-        </is>
-      </c>
-      <c r="F19" s="40" t="inlineStr">
-        <is>
-          <t>总账闭合</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="11">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>注：五类明细含村（城市 5,502 + 村 1,865 = 7,367·命中口径）；行政村 17 村 1,865 条单列（见表D）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1" s="11">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>表C 投诉集中社区 TOP10（城市社区口径）</t>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="11">
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>口径链：全量 43,118 → 有坐标 15,469（ok 9,490+region 5,979）→ ok 可落图 8,562</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="11">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>表C 社区 TOP10（ok 点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="11">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>诉求数</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>占 ok%</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>主要问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="11">
+      <c r="A22" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>港务社区</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>噪声 360、住宅 225、物业 181、停车 144</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" s="11">
-      <c r="A23" s="33" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>投诉条数</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>问题占比%</t>
-        </is>
-      </c>
-      <c r="E23" s="33" t="inlineStr">
-        <is>
-          <t>严重度</t>
-        </is>
-      </c>
-      <c r="F23" s="33" t="inlineStr">
-        <is>
-          <t>主要问题（五类归并）</t>
+      <c r="A23" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>汕头路社区</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>住宅 208、噪声 193、物业 90</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" s="11">
       <c r="A24" s="35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>万达社区</t>
+          <t>宝联社区</t>
         </is>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>414</t>
         </is>
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>8.14</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="F24" s="34" t="inlineStr">
-        <is>
-          <t>噪声 169、停车 83、住宅 75、出行 51、物业 70</t>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="inlineStr">
+        <is>
+          <t>噪声 158、停车 78、物业 72</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" s="11">
       <c r="A25" s="35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>港务社区</t>
+          <t>八一路社区</t>
         </is>
       </c>
       <c r="C25" s="35" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>噪声 100、停车 48、住宅 79、物业 92</t>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>噪声 142、停车 72</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" s="11">
       <c r="A26" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>建设社区</t>
+          <t>东星社区</t>
         </is>
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="F26" s="34" t="inlineStr">
-        <is>
-          <t>噪声 149、停车 23、住宅 88、物业 38</t>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="inlineStr">
+        <is>
+          <t>住宅 73、物业 70</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" s="11">
       <c r="A27" s="35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>岳湾路社区</t>
+          <t>张家湾社区</t>
         </is>
       </c>
       <c r="C27" s="35" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>273</t>
         </is>
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>3.74</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>较严重</t>
-        </is>
-      </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>噪声 89、停车 38、住宅 35、物业 30</t>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>物业 65、停车 62</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" s="11">
       <c r="A28" s="35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
@@ -9051,800 +8223,118 @@
       </c>
       <c r="C28" s="35" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="inlineStr">
-        <is>
-          <t>较严重</t>
-        </is>
-      </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>噪声 66、住宅 68、物业 42</t>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>噪声 109、住宅 76</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" s="11">
       <c r="A29" s="35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>大学路社区</t>
+          <t>魏家湾社区</t>
         </is>
       </c>
       <c r="C29" s="35" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>261</t>
         </is>
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>3.24</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
-        <is>
-          <t>较严重</t>
-        </is>
-      </c>
-      <c r="F29" s="34" t="inlineStr">
-        <is>
-          <t>噪声 72、停车 25、住宅 30、出行 22</t>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>住宅 74</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" s="11">
       <c r="A30" s="35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>张家湾社区</t>
+          <t>艾家嘴社区</t>
         </is>
       </c>
       <c r="C30" s="35" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>231</t>
         </is>
       </c>
       <c r="D30" s="35" t="inlineStr">
         <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>噪声 44、停车 41、物业 35</t>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" s="11">
       <c r="A31" s="35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>宝联社区</t>
+          <t>东站路社区</t>
         </is>
       </c>
       <c r="C31" s="35" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="E31" s="35" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>噪声 43、停车 31、住宅 23</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1" s="11">
-      <c r="A32" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>枫香树社区</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="D32" s="35" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="E32" s="35" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F32" s="34" t="inlineStr">
-        <is>
-          <t>住宅 38、噪声 23、停车 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1" s="11">
-      <c r="A33" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>营盘路社区</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="D33" s="35" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="E33" s="35" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>住宅 34、噪声 32、物业 23</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1" s="11">
-      <c r="A34" s="37" t="inlineStr">
-        <is>
-          <t>严重度分档：占板块 ≥5% 严重 / 3~5% 较严重 / &lt;3% 一般（占比分母 = 城市社区 5,502）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1" s="11">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>表D 行政村民生诉求排行（17 村 · 1,865 条）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1" s="11">
-      <c r="A37" s="33" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>村</t>
-        </is>
-      </c>
-      <c r="C37" s="33" t="inlineStr">
-        <is>
-          <t>诉求数</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="inlineStr">
-        <is>
-          <t>占比%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1" s="11">
-      <c r="A38" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="34" t="inlineStr">
-        <is>
-          <t>共勤村</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="D38" s="35" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1" s="11">
-      <c r="A39" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>旭光村</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="D39" s="35" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1" s="11">
-      <c r="A40" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="B40" s="34" t="inlineStr">
-        <is>
-          <t>汉宜村</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="D40" s="35" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1" s="11">
-      <c r="A41" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>火光村</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D41" s="35" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1" s="11">
-      <c r="A42" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" s="34" t="inlineStr">
-        <is>
-          <t>共和村</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="D42" s="35" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" s="11">
-      <c r="A43" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B43" s="34" t="inlineStr">
-        <is>
-          <t>合益村</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="D43" s="35" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1" s="11">
-      <c r="A44" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="B44" s="34" t="inlineStr">
-        <is>
-          <t>共联村</t>
-        </is>
-      </c>
-      <c r="C44" s="35" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="D44" s="35" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1" s="11">
-      <c r="A45" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="B45" s="34" t="inlineStr">
-        <is>
-          <t>土门村</t>
-        </is>
-      </c>
-      <c r="C45" s="35" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D45" s="35" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1" s="11">
-      <c r="A46" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="B46" s="34" t="inlineStr">
-        <is>
-          <t>共同村</t>
-        </is>
-      </c>
-      <c r="C46" s="35" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D46" s="35" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1" s="11">
-      <c r="A47" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="B47" s="34" t="inlineStr">
-        <is>
-          <t>联丰村</t>
-        </is>
-      </c>
-      <c r="C47" s="35" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D47" s="35" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1" s="11">
-      <c r="A48" s="35" t="n">
-        <v>11</v>
-      </c>
-      <c r="B48" s="34" t="inlineStr">
-        <is>
-          <t>共前村</t>
-        </is>
-      </c>
-      <c r="C48" s="35" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D48" s="35" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" s="11">
-      <c r="A49" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="B49" s="34" t="inlineStr">
-        <is>
-          <t>共升村</t>
-        </is>
-      </c>
-      <c r="C49" s="35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D49" s="35" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1" s="11">
-      <c r="A50" s="35" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="34" t="inlineStr">
-        <is>
-          <t>共强村</t>
-        </is>
-      </c>
-      <c r="C50" s="35" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D50" s="35" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" s="11">
-      <c r="A51" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="B51" s="34" t="inlineStr">
-        <is>
-          <t>梅花村</t>
-        </is>
-      </c>
-      <c r="C51" s="35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D51" s="35" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1" s="11">
-      <c r="A52" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="B52" s="34" t="inlineStr">
-        <is>
-          <t>共谊村</t>
-        </is>
-      </c>
-      <c r="C52" s="35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D52" s="35" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" s="11">
-      <c r="A53" s="35" t="n">
-        <v>16</v>
-      </c>
-      <c r="B53" s="34" t="inlineStr">
-        <is>
-          <t>车站村</t>
-        </is>
-      </c>
-      <c r="C53" s="35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D53" s="35" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" s="11">
-      <c r="A54" s="35" t="n">
-        <v>17</v>
-      </c>
-      <c r="B54" s="34" t="inlineStr">
-        <is>
-          <t>灵宝村</t>
-        </is>
-      </c>
-      <c r="C54" s="35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D54" s="35" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1" s="11">
-      <c r="A55" s="37" t="inlineStr">
-        <is>
-          <t>村口径 = 村内点图层（board=民生基础需求）1,865 条·17 村·占比分母 1,865；18 村中仅 17 村有民生诉求</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1" s="11">
-      <c r="A57" s="32" t="inlineStr">
-        <is>
-          <t>表E 双轨对照（page5 体检结果 ↔ 本页市民反映）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1" s="11">
-      <c r="A58" s="33" t="inlineStr">
-        <is>
-          <t>主题</t>
-        </is>
-      </c>
-      <c r="B58" s="33" t="inlineStr">
-        <is>
-          <t>体检发现（page5）</t>
-        </is>
-      </c>
-      <c r="C58" s="33" t="inlineStr">
-        <is>
-          <t>市民反映（本页）</t>
-        </is>
-      </c>
-      <c r="D58" s="33" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="34" customHeight="1" s="11">
-      <c r="A59" s="35" t="inlineStr">
-        <is>
-          <t>停车</t>
-        </is>
-      </c>
-      <c r="B59" s="34" t="inlineStr">
-        <is>
-          <t>泊位 140 处/充电桩 84 处/电动车 50 个</t>
-        </is>
-      </c>
-      <c r="C59" s="34" t="inlineStr">
-        <is>
-          <t>814 条（收费/私设/乱停放）</t>
-        </is>
-      </c>
-      <c r="D59" s="38" t="n"/>
-      <c r="E59" s="34" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="34" customHeight="1" s="11">
-      <c r="A60" s="35" t="inlineStr">
-        <is>
-          <t>住宅</t>
-        </is>
-      </c>
-      <c r="B60" s="34" t="inlineStr">
-        <is>
-          <t>非成套 31 处/适老化 39 处</t>
-        </is>
-      </c>
-      <c r="C60" s="34" t="inlineStr">
-        <is>
-          <t>1,303 条（老旧改造/质量/防水）</t>
-        </is>
-      </c>
-      <c r="D60" s="38" t="n"/>
-      <c r="E60" s="34" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="34" customHeight="1" s="11">
-      <c r="A61" s="35" t="inlineStr">
-        <is>
-          <t>物业</t>
-        </is>
-      </c>
-      <c r="B61" s="34" t="inlineStr">
-        <is>
-          <t>未物业小区 273 个/乱停放 5 处</t>
-        </is>
-      </c>
-      <c r="C61" s="34" t="inlineStr">
-        <is>
-          <t>1,008 条</t>
-        </is>
-      </c>
-      <c r="D61" s="38" t="n"/>
-      <c r="E61" s="34" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="34" customHeight="1" s="11">
-      <c r="A62" s="35" t="inlineStr">
-        <is>
-          <t>公服设施</t>
-        </is>
-      </c>
-      <c r="B62" s="34" t="inlineStr">
-        <is>
-          <t>养老/托育/幼儿园/学位 8 项缺口</t>
-        </is>
-      </c>
-      <c r="C62" s="34" t="inlineStr">
-        <is>
-          <t>136 条（诉求较少）</t>
-        </is>
-      </c>
-      <c r="D62" s="38" t="n"/>
-      <c r="E62" s="34" t="inlineStr">
-        <is>
-          <t>◐ 体检独证（学位/养老缺口市民直接诉求少·多为规划配置问题）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="34" customHeight="1" s="11">
-      <c r="A63" s="35" t="inlineStr">
-        <is>
-          <t>出行</t>
-        </is>
-      </c>
-      <c r="B63" s="34" t="inlineStr">
-        <is>
-          <t>不达标步行道 2.09 千米</t>
-        </is>
-      </c>
-      <c r="C63" s="34" t="inlineStr">
-        <is>
-          <t>586 条（道路通行/公交）</t>
-        </is>
-      </c>
-      <c r="D63" s="38" t="n"/>
-      <c r="E63" s="34" t="inlineStr">
-        <is>
-          <t>✓ 相关印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="34" customHeight="1" s="11">
-      <c r="A64" s="35" t="inlineStr">
-        <is>
-          <t>（体检无对应）</t>
-        </is>
-      </c>
-      <c r="B64" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C64" s="34" t="inlineStr">
-        <is>
-          <t>噪声 1,791 条</t>
-        </is>
-      </c>
-      <c r="D64" s="38" t="n"/>
-      <c r="E64" s="34" t="inlineStr">
-        <is>
-          <t>◑ 市民独证（噪声是体检盲区·民生诉求最大类）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1" s="11">
-      <c r="A67" s="32" t="inlineStr">
-        <is>
-          <t>表F 口径详注</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1" s="11">
-      <c r="A68" s="37" t="inlineStr">
-        <is>
-          <t>① 承接 page2 线二：83.3% 属于底线与民生（47,693 件）中民生基础 = 42,871 件（三层定稿·74.9%）；本页主体用命中口径（城市 5,502 + 村 1,865 = 7,367）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1" s="11">
-      <c r="A69" s="37" t="inlineStr">
-        <is>
-          <t>② 五类归并（用户定稿）：噪声=噪声治理+施工管理+街面秩序；停车=停车设施；住宅=住房+城市更新；出行=交通设施+市政管网；物业=物业管理+环境治理+公服设施</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1" s="11">
-      <c r="A70" s="37" t="inlineStr">
-        <is>
-          <t>③ 社区口径：城市社区 148（CSV 实测）+ 行政村 17（18 村中 17 村有民生诉求）= 165；与 page4 的“126 城市社区+18 村”同法拆分</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1" s="11">
-      <c r="A71" s="37" t="inlineStr">
-        <is>
-          <t>④ 占比分母：城市社区 5,502（表A/C）·村 1,865（表D）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1" s="11">
-      <c r="A72" s="37" t="inlineStr">
-        <is>
-          <t>⑤ 数据审计：旧素材 7,340/165 含村口径已按实测修正（城市 5,502 + 村 1,865 = 7,367·与旧 7,340 差 27 条为源数据漂移）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1" s="11">
-      <c r="A73" s="37" t="inlineStr">
-        <is>
-          <t>⑥ 数据源红线：中转站真实数据·sim 禁入</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1" s="11">
-      <c r="A75" s="37" t="inlineStr">
-        <is>
-          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v2）· 制作：Codex · 2026-08-13</t>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>出行 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" s="11">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>行政村（ok）：火光村 89、旭光村 25、联丰村 15、共升村 13、共勤村 8、共联村 8、共谊村 5、灵宝村 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1" s="11">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>数据源：12345_治理清洗版+checkup 治理产出（CB-30）· 社区/村/区级分级 · 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A36:I36"/>
+  <mergeCells count="7">
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A67:I67"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A72:I72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -4689,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
@@ -5049,14 +5049,14 @@
     <row r="17" ht="30" customHeight="1" s="11">
       <c r="A17" s="37" t="inlineStr">
         <is>
-          <t>口径链：全量 5,005 → 有坐标 2,657（ok 1,713+region 944）→ ok 可落图 1,529</t>
+          <t>口径链：全量 5,005 → 有坐标 2,657（ok 1,713 + region 944）→ ok 可落图 1,529（社区 1,491 + 村 38）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="11">
       <c r="A18" s="32" t="inlineStr">
         <is>
-          <t>表C 社区 TOP8（ok 点）</t>
+          <t>表C 社区 TOP8（ok 点·社区口径）</t>
         </is>
       </c>
     </row>
@@ -5287,29 +5287,328 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" s="11">
-      <c r="A28" s="37" t="inlineStr">
-        <is>
-          <t>行政村（ok）：火光村 14、共升村 10、灵宝村 4、旭光村 3、共勤村 2、联丰村 2、共联村 2、共前村 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1" s="11">
-      <c r="A29" s="37" t="inlineStr">
-        <is>
-          <t>数据源：12345_治理清洗版+checkup 治理产出（CB-30）· 社区/村/区级分级 · 制作：Codex · 2026-08-13</t>
+    <row r="29" ht="20" customHeight="1" s="11">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>表D 行政村诉求排行（ok 点·村口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" s="11">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>诉求数</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" s="11">
+      <c r="A31" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>火光村</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" s="11">
+      <c r="A32" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>共升村</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" s="11">
+      <c r="A33" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>灵宝村</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" s="11">
+      <c r="A34" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>旭光村</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" s="11">
+      <c r="A35" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>共勤村</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" s="11">
+      <c r="A36" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>联丰村</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" s="11">
+      <c r="A37" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>共联村</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" s="11">
+      <c r="A38" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>共前村</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="11">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>表E 双轨对照（page3 体检结果 ↔ 本页市民反映）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" s="11">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>主题</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>体检发现（page3）</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>市民反映（本页）</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1" s="11">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>管网安全</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>燃气 6 栋 + 管线 186 栋</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>774 条</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="n"/>
+      <c r="E42" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1" s="11">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>消防安全</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>楼道隐患 240 栋</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>179 条</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="n"/>
+      <c r="E43" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1" s="11">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>环境安全</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>结构 42 + 围护 454（堡坎）</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>20 条</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="n"/>
+      <c r="E44" s="34" t="inlineStr">
+        <is>
+          <t>◐ 体检独证</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1" s="11">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>出行安全</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>（体检无对应）</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>556 条</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="n"/>
+      <c r="E45" s="34" t="inlineStr">
+        <is>
+          <t>◑ 市民独证</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" s="11">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>表F 口径详注</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1" s="11">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1" s="11">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t>② 三级分级：ok 可落图（社区/村 sjoin）/ region 仅区级 / miss 不落</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1" s="11">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>③ 社区与村分别统计，不混淆</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1" s="11">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>④ 全量（投诉+求助）5,005 = 有坐标 2,657 + 无坐标（miss）约 2,348</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1" s="11">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v3）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
     <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A51:I51"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A47:I47"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A48:I48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7605,7 +7904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
@@ -8024,14 +8323,14 @@
     <row r="19" ht="30" customHeight="1" s="11">
       <c r="A19" s="37" t="inlineStr">
         <is>
-          <t>口径链：全量 43,118 → 有坐标 15,469（ok 9,490+region 5,979）→ ok 可落图 8,562</t>
+          <t>口径链：全量 43,118 → 有坐标 15,469（ok 9,490 + region 5,979）→ ok 可落图 8,562（社区 8,394 + 村 168）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" s="11">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>表C 社区 TOP10（ok 点）</t>
+          <t>表C 社区 TOP10（ok 点·社区口径）</t>
         </is>
       </c>
     </row>
@@ -8312,29 +8611,351 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="11">
-      <c r="A32" s="37" t="inlineStr">
-        <is>
-          <t>行政村（ok）：火光村 89、旭光村 25、联丰村 15、共升村 13、共勤村 8、共联村 8、共谊村 5、灵宝村 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1" s="11">
-      <c r="A33" s="37" t="inlineStr">
-        <is>
-          <t>数据源：12345_治理清洗版+checkup 治理产出（CB-30）· 社区/村/区级分级 · 制作：Codex · 2026-08-13</t>
+    <row r="33" ht="20" customHeight="1" s="11">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>表D 行政村诉求排行（ok 点·村口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" s="11">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>诉求数</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" s="11">
+      <c r="A35" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>火光村</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" s="11">
+      <c r="A36" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>旭光村</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" s="11">
+      <c r="A37" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>联丰村</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" s="11">
+      <c r="A38" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>共升村</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" s="11">
+      <c r="A39" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>共勤村</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" s="11">
+      <c r="A40" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>共联村</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" s="11">
+      <c r="A41" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>共谊村</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1" s="11">
+      <c r="A42" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>灵宝村</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="11">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>表E 双轨对照（page5 体检结果 ↔ 本页市民反映）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" s="11">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>主题</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>体检发现（page5）</t>
+        </is>
+      </c>
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>市民反映（本页）</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1" s="11">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>停车</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>泊位 140 处/充电桩 84/电动车 50</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>1,312 条</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="n"/>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1" s="11">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>非成套 31/适老化 39</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>1,956 条</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="n"/>
+      <c r="E47" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1" s="11">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>物业</t>
+        </is>
+      </c>
+      <c r="B48" s="34" t="inlineStr">
+        <is>
+          <t>未物业 273 个/乱停放 5</t>
+        </is>
+      </c>
+      <c r="C48" s="34" t="inlineStr">
+        <is>
+          <t>1,535 条</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="n"/>
+      <c r="E48" s="34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1" s="11">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>出行</t>
+        </is>
+      </c>
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>步行道 2.09 千米</t>
+        </is>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>898 条</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="n"/>
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>✓ 相关印证</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1" s="11">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>噪声</t>
+        </is>
+      </c>
+      <c r="B50" s="34" t="inlineStr">
+        <is>
+          <t>（体检无对应）</t>
+        </is>
+      </c>
+      <c r="C50" s="34" t="inlineStr">
+        <is>
+          <t>2,861 条</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n"/>
+      <c r="E50" s="34" t="inlineStr">
+        <is>
+          <t>◑ 市民独证</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" s="11">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>表F 口径详注</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1" s="11">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1" s="11">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>② 三级分级：ok 可落图（社区/村 sjoin）/ region 仅区级 / miss 不落</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1" s="11">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t>③ 社区与村分别统计，不混淆</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1" s="11">
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t>④ 全量（投诉+求助）43,118 = 有坐标 15,469 + 无坐标（miss）约 27,649</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1" s="11">
+      <c r="A57" s="37" t="inlineStr">
+        <is>
+          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v3）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A57:I57"/>
     <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A11:I11"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A44:I44"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -4710,6 +4710,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -4735,7 +4736,7 @@
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>社区/村</t>
+          <t>涉及社区数</t>
         </is>
       </c>
       <c r="E4" s="33" t="inlineStr">
@@ -4767,7 +4768,7 @@
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>762 + 12</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -4799,7 +4800,7 @@
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>538 + 18</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -4831,7 +4832,7 @@
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>171 + 8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -4863,7 +4864,7 @@
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>20 + 0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -4877,6 +4878,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1" s="11">
       <c r="A10" s="32" t="inlineStr">
         <is>
@@ -4892,20 +4894,25 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>ok 社区+村</t>
+          <t>ok 社区</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
+          <t>ok 村</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
           <t>region 区级</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>有坐标合计</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>占 ok%</t>
         </is>
@@ -4919,20 +4926,25 @@
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>762</t>
         </is>
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
           <t>551</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>1,325</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>50.6</t>
         </is>
@@ -4946,20 +4958,25 @@
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>538</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>868</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>36.4</t>
         </is>
@@ -4973,20 +4990,25 @@
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
@@ -5005,15 +5027,20 @@
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
@@ -5027,20 +5054,25 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>1,529</t>
+          <t>1,491</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
           <t>944</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>2,657</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -7925,6 +7957,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -7950,7 +7983,7 @@
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>社区/村</t>
+          <t>涉及社区数</t>
         </is>
       </c>
       <c r="E4" s="33" t="inlineStr">
@@ -7982,7 +8015,7 @@
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>2,807 + 54</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -8014,7 +8047,7 @@
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>1,291 + 21</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -8046,7 +8079,7 @@
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>1,934 + 22</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -8078,7 +8111,7 @@
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>867 + 31</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -8110,7 +8143,7 @@
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>1,495 + 40</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -8124,6 +8157,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1" s="11">
       <c r="A11" s="32" t="inlineStr">
         <is>
@@ -8139,20 +8173,25 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>ok 社区+村</t>
+          <t>ok 社区</t>
         </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
+          <t>ok 村</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
           <t>region 区级</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>有坐标合计</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>占 ok%</t>
         </is>
@@ -8166,20 +8205,25 @@
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>2,861</t>
+          <t>2,807</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
           <t>1,674</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>4,535</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>33.4</t>
         </is>
@@ -8193,20 +8237,25 @@
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>1,312</t>
+          <t>1,291</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
           <t>1,087</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>2,399</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
@@ -8220,20 +8269,25 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>1,956</t>
+          <t>1,934</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
           <t>1,334</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>3,290</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
@@ -8247,20 +8301,25 @@
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>867</t>
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
           <t>664</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>1,562</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>10.5</t>
         </is>
@@ -8274,20 +8333,25 @@
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>1,535</t>
+          <t>1,495</t>
         </is>
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
           <t>1,220</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>2,755</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="F17" s="35" t="inlineStr">
         <is>
           <t>17.9</t>
         </is>
@@ -8301,20 +8365,25 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>8,562</t>
+          <t>8,394</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
           <t>5,979</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>14,541</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>100</t>
         </is>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -4689,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
@@ -4710,11 +4710,10 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>表A 4 类问题明细（ok 可落图·社区+村）</t>
+          <t>表A 4 类问题明细（精确可落图·社区+村）</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4730,7 @@
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>占 ok%</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
@@ -4763,7 +4762,7 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
@@ -4795,7 +4794,7 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
@@ -4805,7 +4804,7 @@
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
-          <t>主要为道路破损、桥梁损坏、交通设施故障</t>
+          <t>主要为交通信号灯、人行道、车行道等设施破损</t>
         </is>
       </c>
       <c r="F6" s="34" t="inlineStr">
@@ -4827,7 +4826,7 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
@@ -4837,7 +4836,7 @@
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
-          <t>主要为消防通道占用、器材缺失</t>
+          <t>主要为消防通道占用、消防器材缺失</t>
         </is>
       </c>
       <c r="F7" s="34" t="inlineStr">
@@ -4859,7 +4858,7 @@
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
@@ -4878,11 +4877,10 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="20" customHeight="1" s="11">
       <c r="A10" s="32" t="inlineStr">
         <is>
-          <t>表B 规模总表（有坐标分级）</t>
+          <t>表B 规模总表（分级：精确/区级质心）</t>
         </is>
       </c>
     </row>
@@ -4894,17 +4892,17 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>ok 社区</t>
+          <t>精确社区</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>ok 村</t>
+          <t>精确村</t>
         </is>
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
-          <t>region 区级</t>
+          <t>区级质心</t>
         </is>
       </c>
       <c r="E11" s="33" t="inlineStr">
@@ -4914,7 +4912,7 @@
       </c>
       <c r="F11" s="33" t="inlineStr">
         <is>
-          <t>占 ok%</t>
+          <t>占比</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4944,7 @@
       </c>
       <c r="F12" s="35" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4976,7 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5008,7 @@
       </c>
       <c r="F14" s="35" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5040,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -5074,21 +5072,21 @@
       </c>
       <c r="F16" s="33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="11">
       <c r="A17" s="37" t="inlineStr">
         <is>
-          <t>口径链：全量 5,005 → 有坐标 2,657（ok 1,713 + region 944）→ ok 可落图 1,529（社区 1,491 + 村 38）</t>
+          <t>口径链：全量 5,005 → 有坐标 2,657（精确 1,713 + 区级质心 944）→ 精确可落图 1,529（社区 1,491 + 村 38）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="11">
       <c r="A18" s="32" t="inlineStr">
         <is>
-          <t>表C 社区 TOP8（ok 点·社区口径）</t>
+          <t>表C 社区 TOP10（精确点·社区口径）</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5108,7 @@
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>占 ok%</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="E19" s="33" t="inlineStr">
@@ -5135,7 +5133,7 @@
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="E20" s="34" t="inlineStr">
@@ -5160,12 +5158,12 @@
       </c>
       <c r="D21" s="35" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>管网 50、出行安全 30</t>
+          <t>管网 50、出行安全 30、消防 8</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5183,7 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -5210,12 +5208,12 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>管网 26、消防 11</t>
+          <t>管网 26、出行安全 10、消防 11</t>
         </is>
       </c>
     </row>
@@ -5235,12 +5233,12 @@
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>管网 25</t>
+          <t>管网 25、出行安全 18、消防 2</t>
         </is>
       </c>
     </row>
@@ -5260,12 +5258,12 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>出行安全 19</t>
+          <t>管网 17、出行安全 19、消防 5</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5283,12 @@
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>出行安全 20</t>
+          <t>管网 18、出行安全 20</t>
         </is>
       </c>
     </row>
@@ -5310,136 +5308,156 @@
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>消防 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1" s="11">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>表D 行政村诉求排行（ok 点·村口径）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1" s="11">
-      <c r="A30" s="33" t="inlineStr">
+          <t>管网 12、出行安全 15、消防 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" s="11">
+      <c r="A28" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>朝阳路社区</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>管网 18、出行安全 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" s="11">
+      <c r="A29" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>香锦社区</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>管网 20、出行安全 11、消防 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="11">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>表D 行政村诉求排行（精确点·村口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" s="11">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>排序</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>村</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>诉求数</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1" s="11">
-      <c r="A31" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>火光村</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1" s="11">
-      <c r="A32" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>共升村</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" s="11">
       <c r="A33" s="35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>灵宝村</t>
+          <t>火光村</t>
         </is>
       </c>
       <c r="C33" s="35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" s="11">
       <c r="A34" s="35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>旭光村</t>
+          <t>共升村</t>
         </is>
       </c>
       <c r="C34" s="35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" s="11">
       <c r="A35" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>共勤村</t>
+          <t>灵宝村</t>
         </is>
       </c>
       <c r="C35" s="35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" s="11">
       <c r="A36" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>联丰村</t>
+          <t>旭光村</t>
         </is>
       </c>
       <c r="C36" s="35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" s="11">
       <c r="A37" s="35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>共联村</t>
+          <t>共勤村</t>
         </is>
       </c>
       <c r="C37" s="35" t="inlineStr">
@@ -5450,197 +5468,227 @@
     </row>
     <row r="38" ht="22" customHeight="1" s="11">
       <c r="A38" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>联丰村</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" s="11">
+      <c r="A39" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>共联村</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" s="11">
+      <c r="A40" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>共前村</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C40" s="35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1" s="11">
-      <c r="A40" s="32" t="inlineStr">
+    <row r="42" ht="20" customHeight="1" s="11">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t>表E 双轨对照（page3 体检结果 ↔ 本页市民反映）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1" s="11">
-      <c r="A41" s="33" t="inlineStr">
+    <row r="43" ht="22" customHeight="1" s="11">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>主题</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>体检发现（page3）</t>
         </is>
       </c>
-      <c r="C41" s="33" t="inlineStr">
+      <c r="C43" s="33" t="inlineStr">
         <is>
           <t>市民反映（本页）</t>
         </is>
       </c>
-      <c r="D41" s="33" t="inlineStr">
+      <c r="D43" s="33" t="inlineStr">
         <is>
           <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="26" customHeight="1" s="11">
-      <c r="A42" s="35" t="inlineStr">
-        <is>
-          <t>管网安全</t>
-        </is>
-      </c>
-      <c r="B42" s="34" t="inlineStr">
-        <is>
-          <t>燃气 6 栋 + 管线 186 栋</t>
-        </is>
-      </c>
-      <c r="C42" s="34" t="inlineStr">
-        <is>
-          <t>774 条</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="n"/>
-      <c r="E42" s="34" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="26" customHeight="1" s="11">
-      <c r="A43" s="35" t="inlineStr">
-        <is>
-          <t>消防安全</t>
-        </is>
-      </c>
-      <c r="B43" s="34" t="inlineStr">
-        <is>
-          <t>楼道隐患 240 栋</t>
-        </is>
-      </c>
-      <c r="C43" s="34" t="inlineStr">
-        <is>
-          <t>179 条</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="n"/>
-      <c r="E43" s="34" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1" s="11">
       <c r="A44" s="35" t="inlineStr">
         <is>
-          <t>环境安全</t>
+          <t>管网安全</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>结构 42 + 围护 454（堡坎）</t>
+          <t>燃气 6 栋 + 管线 186 栋</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>20 条</t>
+          <t>774 条</t>
         </is>
       </c>
       <c r="D44" s="38" t="n"/>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>◐ 体检独证</t>
+          <t>✓ 双证聚焦</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1" s="11">
       <c r="A45" s="35" t="inlineStr">
         <is>
-          <t>出行安全</t>
+          <t>消防安全</t>
         </is>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>（体检无对应）</t>
+          <t>楼道隐患 240 栋</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>556 条</t>
+          <t>179 条</t>
         </is>
       </c>
       <c r="D45" s="38" t="n"/>
       <c r="E45" s="34" t="inlineStr">
         <is>
+          <t>✓ 双证聚焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1" s="11">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>环境安全</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>结构 42 + 围护 454（堡坎）</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>20 条</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="n"/>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>◐ 体检独证</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1" s="11">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>出行安全</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>（体检无对应）</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>556 条</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="n"/>
+      <c r="E47" s="34" t="inlineStr">
+        <is>
           <t>◑ 市民独证</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1" s="11">
-      <c r="A47" s="32" t="inlineStr">
+    <row r="49" ht="20" customHeight="1" s="11">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>表F 口径详注</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1" s="11">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1" s="11">
-      <c r="A49" s="37" t="inlineStr">
-        <is>
-          <t>② 三级分级：ok 可落图（社区/村 sjoin）/ region 仅区级 / miss 不落</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="11">
       <c r="A50" s="37" t="inlineStr">
         <is>
-          <t>③ 社区与村分别统计，不混淆</t>
+          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="11">
       <c r="A51" s="37" t="inlineStr">
         <is>
-          <t>④ 全量（投诉+求助）5,005 = 有坐标 2,657 + 无坐标（miss）约 2,348</t>
+          <t>② 分级：精确（高德 geocode 精确命中坐标·可落图）/ 区级质心（区级兜底坐标·仅区级统计）/ 无坐标（miss·不落图）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="11">
       <c r="A52" s="37" t="inlineStr">
         <is>
+          <t>③ 社区与村分别统计，不混淆</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1" s="11">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>④ 全量（投诉+求助）5,005 = 有坐标 2,657 + 无坐标约 2,348</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1" s="11">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
           <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v3）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A52:I52"/>
     <mergeCell ref="A49:I49"/>
     <mergeCell ref="A51:I51"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7978,7 +8026,7 @@
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>占 ok%</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
@@ -8173,17 +8221,17 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>ok 社区</t>
+          <t>精确社区</t>
         </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
-          <t>ok 村</t>
+          <t>精确村</t>
         </is>
       </c>
       <c r="D12" s="33" t="inlineStr">
         <is>
-          <t>region 区级</t>
+          <t>区级质心</t>
         </is>
       </c>
       <c r="E12" s="33" t="inlineStr">
@@ -8193,7 +8241,7 @@
       </c>
       <c r="F12" s="33" t="inlineStr">
         <is>
-          <t>占 ok%</t>
+          <t>占比</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8469,7 @@
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
-          <t>占 ok%</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="E21" s="33" t="inlineStr">
@@ -8680,6 +8728,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="20" customHeight="1" s="11">
       <c r="A33" s="32" t="inlineStr">
         <is>
@@ -8824,6 +8873,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44" ht="20" customHeight="1" s="11">
       <c r="A44" s="32" t="inlineStr">
         <is>
@@ -8968,6 +9018,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="20" customHeight="1" s="11">
       <c r="A52" s="32" t="inlineStr">
         <is>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -5390,6 +5390,11 @@
           <t>诉求数</t>
         </is>
       </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1" s="11">
       <c r="A33" s="35" t="n">
@@ -5405,6 +5410,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1" s="11">
       <c r="A34" s="35" t="n">
@@ -5420,6 +5430,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1" s="11">
       <c r="A35" s="35" t="n">
@@ -5435,6 +5450,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="D35" s="35" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1" s="11">
       <c r="A36" s="35" t="n">
@@ -5450,6 +5470,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>7.9%</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1" s="11">
       <c r="A37" s="35" t="n">
@@ -5465,6 +5490,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1" s="11">
       <c r="A38" s="35" t="n">
@@ -5480,6 +5510,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="22" customHeight="1" s="11">
       <c r="A39" s="35" t="n">
@@ -5495,6 +5530,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="22" customHeight="1" s="11">
       <c r="A40" s="35" t="n">
@@ -5508,6 +5548,11 @@
       <c r="C40" s="35" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8777,7 @@
     <row r="33" ht="20" customHeight="1" s="11">
       <c r="A33" s="32" t="inlineStr">
         <is>
-          <t>表D 行政村诉求排行（ok 点·村口径）</t>
+          <t>表D 行政村诉求排行（精确点·村口径）</t>
         </is>
       </c>
     </row>
@@ -8750,6 +8795,11 @@
       <c r="C34" s="33" t="inlineStr">
         <is>
           <t>诉求数</t>
+        </is>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>占比</t>
         </is>
       </c>
     </row>
@@ -8767,6 +8817,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="D35" s="35" t="inlineStr">
+        <is>
+          <t>53.0%</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1" s="11">
       <c r="A36" s="35" t="n">
@@ -8782,6 +8837,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>14.9%</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1" s="11">
       <c r="A37" s="35" t="n">
@@ -8797,6 +8857,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>8.9%</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1" s="11">
       <c r="A38" s="35" t="n">
@@ -8812,6 +8877,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="22" customHeight="1" s="11">
       <c r="A39" s="35" t="n">
@@ -8827,6 +8897,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="22" customHeight="1" s="11">
       <c r="A40" s="35" t="n">
@@ -8842,6 +8917,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1" s="11">
       <c r="A41" s="35" t="n">
@@ -8857,6 +8937,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1" s="11">
       <c r="A42" s="35" t="n">
@@ -8872,8 +8957,12 @@
           <t>5</t>
         </is>
       </c>
-    </row>
-    <row r="43"/>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="44" ht="20" customHeight="1" s="11">
       <c r="A44" s="32" t="inlineStr">
         <is>
@@ -9018,7 +9107,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52" ht="20" customHeight="1" s="11">
       <c r="A52" s="32" t="inlineStr">
         <is>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -4710,6 +4710,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -4877,6 +4878,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1" s="11">
       <c r="A10" s="32" t="inlineStr">
         <is>
@@ -5367,6 +5369,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="20" customHeight="1" s="11">
       <c r="A31" s="32" t="inlineStr">
         <is>
@@ -5553,6 +5556,26 @@
       <c r="D40" s="35" t="inlineStr">
         <is>
           <t>2.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>共谊村</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8963,6 +8986,26 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>共前村</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="44" ht="20" customHeight="1" s="11">
       <c r="A44" s="32" t="inlineStr">
         <is>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -4710,7 +4710,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -4878,7 +4877,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="20" customHeight="1" s="11">
       <c r="A10" s="32" t="inlineStr">
         <is>
@@ -5369,7 +5367,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="20" customHeight="1" s="11">
       <c r="A31" s="32" t="inlineStr">
         <is>
@@ -8073,7 +8070,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -8126,7 +8122,7 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
@@ -8158,7 +8154,7 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
@@ -8190,7 +8186,7 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
@@ -8222,7 +8218,7 @@
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
@@ -8254,7 +8250,7 @@
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
@@ -8273,7 +8269,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="20" customHeight="1" s="11">
       <c r="A11" s="32" t="inlineStr">
         <is>
@@ -8341,7 +8336,7 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8368,7 @@
       </c>
       <c r="F14" s="35" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8400,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.8%</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8432,7 @@
       </c>
       <c r="F16" s="35" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8464,7 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8496,7 @@
       </c>
       <c r="F18" s="33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8557,7 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -8587,7 +8582,7 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
@@ -8612,7 +8607,7 @@
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
@@ -8637,7 +8632,7 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
@@ -8662,7 +8657,7 @@
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
@@ -8687,7 +8682,7 @@
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -8712,7 +8707,7 @@
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
@@ -8737,7 +8732,7 @@
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
@@ -8762,7 +8757,7 @@
       </c>
       <c r="D30" s="35" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
@@ -8787,7 +8782,7 @@
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
@@ -8796,7 +8791,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="20" customHeight="1" s="11">
       <c r="A33" s="32" t="inlineStr">
         <is>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -109,7 +109,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -315,11 +315,12 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -417,6 +418,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5502,7 +5509,7 @@
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>联丰村</t>
+          <t>共联村</t>
         </is>
       </c>
       <c r="C38" s="35" t="inlineStr">
@@ -5522,7 +5529,7 @@
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>共联村</t>
+          <t>联丰村</t>
         </is>
       </c>
       <c r="C39" s="35" t="inlineStr">
@@ -5557,24 +5564,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>共谊村</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D41" s="35" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="A41" s="41" t="n"/>
+      <c r="B41" s="42" t="n"/>
+      <c r="C41" s="41" t="n"/>
+      <c r="D41" s="41" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="11">
       <c r="A42" s="32" t="inlineStr">
@@ -8981,24 +8974,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="B43" s="34" t="inlineStr">
-        <is>
-          <t>共前村</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D43" s="35" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="A43" s="41" t="n"/>
+      <c r="B43" s="42" t="n"/>
+      <c r="C43" s="41" t="n"/>
+      <c r="D43" s="41" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="11">
       <c r="A44" s="32" t="inlineStr">

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -4720,7 +4720,7 @@
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>表A 4 类问题明细（精确可落图·社区+村）</t>
+          <t>表A 4 类问题明细（命中体检对象·西陵+伍家岗·区级合并）</t>
         </is>
       </c>
     </row>
@@ -4762,20 +4762,16 @@
           <t>管网安全</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
+      <c r="B5" s="35" t="n">
+        <v>1102</v>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>50.6%</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+          <t>54.0%</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>79</v>
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
@@ -4794,20 +4790,16 @@
           <t>出行安全</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
+      <c r="B6" s="35" t="n">
+        <v>723</v>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="D6" s="35" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+          <t>35.4%</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>75</v>
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
@@ -4826,20 +4818,16 @@
           <t>消防安全</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="B7" s="35" t="n">
+        <v>198</v>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>11.7%</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>42</v>
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
@@ -4858,20 +4846,16 @@
           <t>环境安全</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="B8" s="35" t="n">
+        <v>18</v>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="D8" s="35" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>9</v>
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
@@ -4880,14 +4864,14 @@
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>体育场路、黄金卡、福久源、冯家湾、梅子溪</t>
+          <t>体育场路、福久源、茶庵、汕头路、临江坪</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="11">
       <c r="A10" s="32" t="inlineStr">
         <is>
-          <t>表B 规模总表（分级：精确/区级质心）</t>
+          <t>表B 规模总表（命中体检对象·区级视作精准合并）</t>
         </is>
       </c>
     </row>
@@ -4909,12 +4893,12 @@
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
-          <t>区级质心</t>
+          <t>区级+范围外（合并）</t>
         </is>
       </c>
       <c r="E11" s="33" t="inlineStr">
         <is>
-          <t>有坐标合计</t>
+          <t>命中合计</t>
         </is>
       </c>
       <c r="F11" s="33" t="inlineStr">
@@ -4929,29 +4913,21 @@
           <t>管网安全</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="C12" s="35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="E12" s="35" t="inlineStr">
-        <is>
-          <t>1,325</t>
-        </is>
+      <c r="B12" s="35" t="n">
+        <v>669</v>
+      </c>
+      <c r="C12" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>424</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>1102</v>
       </c>
       <c r="F12" s="35" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -4961,29 +4937,21 @@
           <t>出行安全</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="E13" s="35" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
+      <c r="B13" s="35" t="n">
+        <v>466</v>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>245</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>723</v>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.4%</t>
         </is>
       </c>
     </row>
@@ -4993,29 +4961,21 @@
           <t>消防安全</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="E14" s="35" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
+      <c r="B14" s="35" t="n">
+        <v>153</v>
+      </c>
+      <c r="C14" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>37</v>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>198</v>
       </c>
       <c r="F14" s="35" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -5025,29 +4985,21 @@
           <t>环境安全</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="B15" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>18</v>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -5057,25 +5009,17 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>1,491</t>
-        </is>
-      </c>
-      <c r="C16" s="33" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>2,657</t>
-        </is>
+      <c r="B16" s="33" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C16" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>712</v>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>2041</v>
       </c>
       <c r="F16" s="33" t="inlineStr">
         <is>
@@ -5086,7 +5030,7 @@
     <row r="17" ht="30" customHeight="1" s="11">
       <c r="A17" s="37" t="inlineStr">
         <is>
-          <t>口径链：全量 5,005 → 有坐标 2,657（精确 1,713 + 区级质心 944）→ 精确可落图 1,529（社区 1,491 + 村 38）</t>
+          <t>口径链：全量（投诉+求助）5,005 → 有坐标 2,657 → 命中西陵+伍家 2,041（精确社区 1,300 + 村 29 + 区级 691 合并 + 范围外 21）· 范围外（点军/猇亭/夷陵）616 · 无坐标 2,348</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5084,7 @@
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="E20" s="34" t="inlineStr">
@@ -5165,7 +5109,7 @@
       </c>
       <c r="D21" s="35" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
@@ -5190,7 +5134,7 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -5215,7 +5159,7 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
@@ -5240,7 +5184,7 @@
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
@@ -5265,7 +5209,7 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
@@ -5290,7 +5234,7 @@
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
@@ -5315,7 +5259,7 @@
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -5340,7 +5284,7 @@
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
@@ -5365,7 +5309,7 @@
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
@@ -5412,14 +5356,12 @@
           <t>火光村</t>
         </is>
       </c>
-      <c r="C33" s="35" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C33" s="35" t="n">
+        <v>14</v>
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -5429,17 +5371,15 @@
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>共升村</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>灵宝村</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="n">
+        <v>4</v>
       </c>
       <c r="D34" s="35" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -5449,17 +5389,15 @@
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>灵宝村</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>旭光村</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="n">
+        <v>3</v>
       </c>
       <c r="D35" s="35" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -5469,17 +5407,15 @@
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>旭光村</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>共联村</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="D36" s="35" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -5489,17 +5425,15 @@
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>共勤村</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>联丰村</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="D37" s="35" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -5509,17 +5443,15 @@
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>共联村</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>共勤村</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="D38" s="35" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -5529,17 +5461,15 @@
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>联丰村</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>共升村</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -5552,14 +5482,12 @@
           <t>共前村</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C40" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -5609,10 +5537,8 @@
           <t>燃气 6 栋 + 管线 186 栋</t>
         </is>
       </c>
-      <c r="C44" s="34" t="inlineStr">
-        <is>
-          <t>774 条</t>
-        </is>
+      <c r="C44" s="34" t="n">
+        <v>1102</v>
       </c>
       <c r="D44" s="38" t="n"/>
       <c r="E44" s="34" t="inlineStr">
@@ -5632,10 +5558,8 @@
           <t>楼道隐患 240 栋</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
-        <is>
-          <t>179 条</t>
-        </is>
+      <c r="C45" s="34" t="n">
+        <v>198</v>
       </c>
       <c r="D45" s="38" t="n"/>
       <c r="E45" s="34" t="inlineStr">
@@ -5655,10 +5579,8 @@
           <t>结构 42 + 围护 454（堡坎）</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
-        <is>
-          <t>20 条</t>
-        </is>
+      <c r="C46" s="34" t="n">
+        <v>18</v>
       </c>
       <c r="D46" s="38" t="n"/>
       <c r="E46" s="34" t="inlineStr">
@@ -5678,10 +5600,8 @@
           <t>（体检无对应）</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
-        <is>
-          <t>556 条</t>
-        </is>
+      <c r="C47" s="34" t="n">
+        <v>723</v>
       </c>
       <c r="D47" s="38" t="n"/>
       <c r="E47" s="34" t="inlineStr">
@@ -5707,7 +5627,7 @@
     <row r="51" ht="16" customHeight="1" s="11">
       <c r="A51" s="37" t="inlineStr">
         <is>
-          <t>② 分级：精确（高德 geocode 精确命中坐标·可落图）/ 区级质心（区级兜底坐标·仅区级统计）/ 无坐标（miss·不落图）</t>
+          <t>② 命中体检对象 = 西陵区+伍家岗区（12345_西陵+伍家岗.geojson）；区级点（区质心）视作精准合并；分级 = 精确社区 / 精确村 / 区级+范围外（非社区村面）</t>
         </is>
       </c>
     </row>
@@ -5721,14 +5641,14 @@
     <row r="53" ht="16" customHeight="1" s="11">
       <c r="A53" s="37" t="inlineStr">
         <is>
-          <t>④ 全量（投诉+求助）5,005 = 有坐标 2,657 + 无坐标约 2,348</t>
+          <t>④ 全量（投诉+求助）5,005 = 命中西陵+伍家 2,041 + 范围外（点军/猇亭/夷陵）616 + 无坐标 2,348</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="11">
       <c r="A54" s="37" t="inlineStr">
         <is>
-          <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v3）· 制作：Codex · 2026-08-13</t>
+          <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v4·命中西陵+伍家）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8066,7 +7986,7 @@
     <row r="3" ht="20" customHeight="1" s="11">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>表A 5 类问题明细（ok 可落图·社区+村）</t>
+          <t>表A 5 类问题明细（命中体检对象·西陵+伍家岗·区级合并）</t>
         </is>
       </c>
     </row>
@@ -8108,20 +8028,16 @@
           <t>噪声</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
-        <is>
-          <t>2,861</t>
-        </is>
+      <c r="B5" s="35" t="n">
+        <v>3689</v>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>33.4%</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+          <t>32.5%</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>92</v>
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
@@ -8140,20 +8056,16 @@
           <t>停车</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>1,312</t>
-        </is>
+      <c r="B6" s="35" t="n">
+        <v>1870</v>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>15.3%</t>
-        </is>
-      </c>
-      <c r="D6" s="35" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+          <t>16.5%</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>83</v>
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
@@ -8172,20 +8084,16 @@
           <t>住宅</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>1,956</t>
-        </is>
+      <c r="B7" s="35" t="n">
+        <v>2466</v>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>22.8%</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>91</v>
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
@@ -8204,20 +8112,16 @@
           <t>出行</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
+      <c r="B8" s="35" t="n">
+        <v>1027</v>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-      <c r="D8" s="35" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>85</v>
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
@@ -8236,20 +8140,16 @@
           <t>物业</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>1,535</t>
-        </is>
+      <c r="B9" s="35" t="n">
+        <v>2296</v>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>93</v>
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
@@ -8265,7 +8165,7 @@
     <row r="11" ht="20" customHeight="1" s="11">
       <c r="A11" s="32" t="inlineStr">
         <is>
-          <t>表B 规模总表（有坐标分级）</t>
+          <t>表B 规模总表（命中体检对象·区级视作精准合并）</t>
         </is>
       </c>
     </row>
@@ -8287,12 +8187,12 @@
       </c>
       <c r="D12" s="33" t="inlineStr">
         <is>
-          <t>区级质心</t>
+          <t>区级+范围外（合并）</t>
         </is>
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
-          <t>有坐标合计</t>
+          <t>命中合计</t>
         </is>
       </c>
       <c r="F12" s="33" t="inlineStr">
@@ -8307,29 +8207,21 @@
           <t>噪声</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>2,807</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="inlineStr">
-        <is>
-          <t>1,674</t>
-        </is>
-      </c>
-      <c r="E13" s="35" t="inlineStr">
-        <is>
-          <t>4,535</t>
-        </is>
+      <c r="B13" s="35" t="n">
+        <v>2502</v>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>54</v>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>3689</v>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.5%</t>
         </is>
       </c>
     </row>
@@ -8339,29 +8231,21 @@
           <t>停车</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>1,291</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="inlineStr">
-        <is>
-          <t>1,087</t>
-        </is>
-      </c>
-      <c r="E14" s="35" t="inlineStr">
-        <is>
-          <t>2,399</t>
-        </is>
+      <c r="B14" s="35" t="n">
+        <v>1143</v>
+      </c>
+      <c r="C14" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>712</v>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>1870</v>
       </c>
       <c r="F14" s="35" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -8371,29 +8255,21 @@
           <t>住宅</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>1,934</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>1,334</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="inlineStr">
-        <is>
-          <t>3,290</t>
-        </is>
+      <c r="B15" s="35" t="n">
+        <v>1688</v>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>758</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>2466</v>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -8403,29 +8279,21 @@
           <t>出行</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>1,562</t>
-        </is>
+      <c r="B16" s="35" t="n">
+        <v>730</v>
+      </c>
+      <c r="C16" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>269</v>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>1027</v>
       </c>
       <c r="F16" s="35" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -8435,29 +8303,21 @@
           <t>物业</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>1,495</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="inlineStr">
-        <is>
-          <t>1,220</t>
-        </is>
-      </c>
-      <c r="E17" s="35" t="inlineStr">
-        <is>
-          <t>2,755</t>
-        </is>
+      <c r="B17" s="35" t="n">
+        <v>1351</v>
+      </c>
+      <c r="C17" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>910</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>2296</v>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -8467,25 +8327,17 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>8,394</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>5,979</t>
-        </is>
-      </c>
-      <c r="E18" s="33" t="inlineStr">
-        <is>
-          <t>14,541</t>
-        </is>
+      <c r="B18" s="33" t="n">
+        <v>7414</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>152</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>3782</v>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>11348</v>
       </c>
       <c r="F18" s="33" t="inlineStr">
         <is>
@@ -8496,7 +8348,7 @@
     <row r="19" ht="30" customHeight="1" s="11">
       <c r="A19" s="37" t="inlineStr">
         <is>
-          <t>口径链：全量 43,118 → 有坐标 15,469（ok 9,490 + region 5,979）→ ok 可落图 8,562（社区 8,394 + 村 168）</t>
+          <t>口径链：全量（投诉+求助）43,118 → 有坐标 15,469 → 命中西陵+伍家 11,348（精确社区 7,414 + 村 152 + 区级 3,697 合并 + 范围外 85）· 范围外（点军/猇亭/夷陵）4,121 · 无坐标 27,649</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8402,7 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -8575,7 +8427,7 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
@@ -8600,7 +8452,7 @@
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
@@ -8625,7 +8477,7 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
@@ -8650,7 +8502,7 @@
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
@@ -8675,7 +8527,7 @@
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -8700,7 +8552,7 @@
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
@@ -8725,7 +8577,7 @@
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
@@ -8750,7 +8602,7 @@
       </c>
       <c r="D30" s="35" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
@@ -8775,7 +8627,7 @@
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
@@ -8822,14 +8674,12 @@
           <t>火光村</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="C35" s="35" t="n">
+        <v>89</v>
       </c>
       <c r="D35" s="35" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -8842,14 +8692,12 @@
           <t>旭光村</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="C36" s="35" t="n">
+        <v>25</v>
       </c>
       <c r="D36" s="35" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -8862,14 +8710,12 @@
           <t>联丰村</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C37" s="35" t="n">
+        <v>15</v>
       </c>
       <c r="D37" s="35" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -8879,17 +8725,15 @@
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>共升村</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>共联村</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="D38" s="35" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -8902,14 +8746,12 @@
           <t>共勤村</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C39" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -8919,17 +8761,15 @@
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>共联村</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>共谊村</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="n">
+        <v>5</v>
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -8939,17 +8779,15 @@
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>共谊村</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>灵宝村</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -9019,10 +8857,8 @@
           <t>泊位 140 处/充电桩 84/电动车 50</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
-        <is>
-          <t>1,312 条</t>
-        </is>
+      <c r="C46" s="34" t="n">
+        <v>1870</v>
       </c>
       <c r="D46" s="38" t="n"/>
       <c r="E46" s="34" t="inlineStr">
@@ -9042,10 +8878,8 @@
           <t>非成套 31/适老化 39</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
-        <is>
-          <t>1,956 条</t>
-        </is>
+      <c r="C47" s="34" t="n">
+        <v>2466</v>
       </c>
       <c r="D47" s="38" t="n"/>
       <c r="E47" s="34" t="inlineStr">
@@ -9065,10 +8899,8 @@
           <t>未物业 273 个/乱停放 5</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
-        <is>
-          <t>1,535 条</t>
-        </is>
+      <c r="C48" s="34" t="n">
+        <v>2296</v>
       </c>
       <c r="D48" s="38" t="n"/>
       <c r="E48" s="34" t="inlineStr">
@@ -9088,10 +8920,8 @@
           <t>步行道 2.09 千米</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr">
-        <is>
-          <t>898 条</t>
-        </is>
+      <c r="C49" s="34" t="n">
+        <v>1027</v>
       </c>
       <c r="D49" s="38" t="n"/>
       <c r="E49" s="34" t="inlineStr">
@@ -9111,10 +8941,8 @@
           <t>（体检无对应）</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
-        <is>
-          <t>2,861 条</t>
-        </is>
+      <c r="C50" s="34" t="n">
+        <v>3689</v>
       </c>
       <c r="D50" s="38" t="n"/>
       <c r="E50" s="34" t="inlineStr">
@@ -9140,7 +8968,7 @@
     <row r="54" ht="16" customHeight="1" s="11">
       <c r="A54" s="37" t="inlineStr">
         <is>
-          <t>② 三级分级：ok 可落图（社区/村 sjoin）/ region 仅区级 / miss 不落</t>
+          <t>② 命中体检对象 = 西陵区+伍家岗区（12345_西陵+伍家岗.geojson）；区级点（区质心）视作精准合并；分级 = 精确社区 / 精确村 / 区级+范围外（非社区村面）</t>
         </is>
       </c>
     </row>
@@ -9154,14 +8982,14 @@
     <row r="56" ht="16" customHeight="1" s="11">
       <c r="A56" s="37" t="inlineStr">
         <is>
-          <t>④ 全量（投诉+求助）43,118 = 有坐标 15,469 + 无坐标（miss）约 27,649</t>
+          <t>④ 全量（投诉+求助）43,118 = 命中西陵+伍家 11,348 + 范围外（点军/猇亭/夷陵）4,121 + 无坐标 27,649</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="11">
       <c r="A57" s="37" t="inlineStr">
         <is>
-          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v3）· 制作：Codex · 2026-08-13</t>
+          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v4·命中西陵+伍家）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -99,6 +99,9 @@
     <font>
       <name val="微软雅黑"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -320,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -424,6 +427,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4711,16 +4721,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="11">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>安全韧性问题 · 市民反映（page4）</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>表A 4 类问题明细（命中体检对象·西陵+伍家岗·区级合并）</t>
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>表A 4 类问题明细（命中体检对象·西陵+伍家岗·区级合并·社区 sjoin 精确）</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4782,7 @@
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
@@ -4780,7 +4791,7 @@
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>港务、东星、汕头路、花艳、宝联</t>
+          <t>港务、朝阳路、建设、万达、大学路</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4810,7 @@
         </is>
       </c>
       <c r="D6" s="35" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
@@ -4808,7 +4819,7 @@
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>港务、东星、大学路、张家湾、宝联</t>
+          <t>大学路、万达、港务、朝阳路、张家湾</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4838,7 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
@@ -4836,7 +4847,7 @@
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>港务、艾家嘴、魏家湾、汕头路、宝联</t>
+          <t>港务、建设、朝阳路、体育场路、枫香树</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4866,7 @@
         </is>
       </c>
       <c r="D8" s="35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
@@ -4864,12 +4875,13 @@
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>体育场路、福久源、茶庵、汕头路、临江坪</t>
-        </is>
-      </c>
-    </row>
+          <t>体育场路、大学路、朝阳路、建设、肖家岗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1" s="11">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>表B 规模总表（命中体检对象·区级视作精准合并）</t>
         </is>
@@ -4914,13 +4926,13 @@
         </is>
       </c>
       <c r="B12" s="35" t="n">
-        <v>669</v>
+        <v>538</v>
       </c>
       <c r="C12" s="35" t="n">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="D12" s="35" t="n">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E12" s="35" t="n">
         <v>1102</v>
@@ -4938,13 +4950,13 @@
         </is>
       </c>
       <c r="B13" s="35" t="n">
-        <v>466</v>
+        <v>371</v>
       </c>
       <c r="C13" s="35" t="n">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>723</v>
@@ -4962,13 +4974,13 @@
         </is>
       </c>
       <c r="B14" s="35" t="n">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="C14" s="35" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D14" s="35" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E14" s="35" t="n">
         <v>198</v>
@@ -4986,10 +4998,10 @@
         </is>
       </c>
       <c r="B15" s="35" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C15" s="35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15" s="35" t="n">
         <v>6</v>
@@ -5010,13 +5022,13 @@
         </is>
       </c>
       <c r="B16" s="33" t="n">
-        <v>1300</v>
+        <v>1035</v>
       </c>
       <c r="C16" s="33" t="n">
-        <v>29</v>
+        <v>284</v>
       </c>
       <c r="D16" s="33" t="n">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="E16" s="33" t="n">
         <v>2041</v>
@@ -5028,16 +5040,16 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="11">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>口径链：全量（投诉+求助）5,005 → 有坐标 2,657 → 命中西陵+伍家 2,041（精确社区 1,300 + 村 29 + 区级 691 合并 + 范围外 21）· 范围外（点军/猇亭/夷陵）616 · 无坐标 2,348</t>
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>口径链：全量（投诉+求助）5,005 → 有坐标 2,657 → 命中西陵+伍家 2,041（精确社区 1,035 + 村 284 + 区级 691 合并 + 范围外 31）· 范围外（点军/猇亭/夷陵）616 · 无坐标 2,348</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="11">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>表C 社区 TOP10（精确点·社区口径）</t>
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>表C 社区 TOP10（精确点·社区口径·占精确社区 1,035）</t>
         </is>
       </c>
     </row>
@@ -5077,19 +5089,17 @@
           <t>港务社区</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="C20" s="35" t="n">
+        <v>83</v>
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="E20" s="34" t="inlineStr">
         <is>
-          <t>管网 98、出行安全 46、消防 23</t>
+          <t>管网 53、出行安全 17、消防 13</t>
         </is>
       </c>
     </row>
@@ -5099,22 +5109,20 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>东星社区</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+          <t>朝阳路社区</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="n">
+        <v>58</v>
       </c>
       <c r="D21" s="35" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>管网 50、出行安全 30、消防 8</t>
+          <t>管网 33、出行安全 15、消防 9</t>
         </is>
       </c>
     </row>
@@ -5124,22 +5132,20 @@
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>宝联社区</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+          <t>建设社区</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n">
+        <v>52</v>
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
         <is>
-          <t>管网 23、出行安全 18、消防 10</t>
+          <t>管网 27、出行安全 12、消防 12</t>
         </is>
       </c>
     </row>
@@ -5149,22 +5155,20 @@
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>汕头路社区</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+          <t>万达社区</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="n">
+        <v>50</v>
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>管网 26、出行安全 10、消防 11</t>
+          <t>管网 26、出行安全 21、消防 3</t>
         </is>
       </c>
     </row>
@@ -5174,22 +5178,20 @@
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>花艳社区</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>大学路社区</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n">
+        <v>44</v>
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>管网 25、出行安全 18、消防 2</t>
+          <t>出行安全 24、管网 19、环境安全 1</t>
         </is>
       </c>
     </row>
@@ -5199,22 +5201,20 @@
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>张家湾社区</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+          <t>体育场路社区</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="n">
+        <v>29</v>
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>管网 17、出行安全 19、消防 5</t>
+          <t>管网 13、出行安全 7、消防 6</t>
         </is>
       </c>
     </row>
@@ -5224,22 +5224,20 @@
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>大学路社区</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>宝联社区</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="n">
+        <v>29</v>
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>管网 18、出行安全 20</t>
+          <t>管网 18、出行安全 8、消防 3</t>
         </is>
       </c>
     </row>
@@ -5249,22 +5247,20 @@
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>魏家湾社区</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>张家湾社区</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="n">
+        <v>28</v>
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>管网 12、出行安全 15、消防 11</t>
+          <t>管网 13、出行安全 13、消防 2</t>
         </is>
       </c>
     </row>
@@ -5274,22 +5270,20 @@
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>朝阳路社区</t>
-        </is>
-      </c>
-      <c r="C28" s="35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+          <t>伍临路社区</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="n">
+        <v>21</v>
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>管网 18、出行安全 16</t>
+          <t>管网 10、出行安全 8、消防 3</t>
         </is>
       </c>
     </row>
@@ -5299,206 +5293,234 @@
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>香锦社区</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+          <t>绿萝路社区</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="n">
+        <v>20</v>
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>管网 20、出行安全 11、消防 2</t>
+          <t>出行安全 10、管网 9、消防 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>表D 行政村诉求排行（精确点·村口径·top10）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" s="11">
       <c r="A31" s="32" t="inlineStr">
         <is>
-          <t>表D 行政村诉求排行（精确点·村口径）</t>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>诉求数</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>占比</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" s="11">
-      <c r="A32" s="33" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
+      <c r="A32" s="33" t="n">
+        <v>1</v>
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>村</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="inlineStr">
-        <is>
-          <t>诉求数</t>
-        </is>
+          <t>汉宜村</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>86</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" s="11">
       <c r="A33" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>火光村</t>
+          <t>旭光村</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" s="11">
       <c r="A34" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>灵宝村</t>
+          <t>共勤村</t>
         </is>
       </c>
       <c r="C34" s="35" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D34" s="35" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" s="11">
       <c r="A35" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>旭光村</t>
+          <t>共和村</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D35" s="35" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" s="11">
       <c r="A36" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>共联村</t>
+          <t>火光村</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D36" s="35" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" s="11">
       <c r="A37" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>联丰村</t>
+          <t>共联村</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D37" s="35" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" s="11">
       <c r="A38" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>共勤村</t>
+          <t>合益村</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D38" s="35" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" s="11">
       <c r="A39" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>共升村</t>
+          <t>共谊村</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" s="11">
       <c r="A40" s="35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
+          <t>联丰村</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
           <t>共前村</t>
         </is>
       </c>
-      <c r="C40" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="35" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="41" t="n"/>
-      <c r="B41" s="42" t="n"/>
-      <c r="C41" s="41" t="n"/>
-      <c r="D41" s="41" t="n"/>
+      <c r="C41" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="41" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1" s="11">
-      <c r="A42" s="32" t="inlineStr">
+      <c r="A42" s="44" t="inlineStr">
         <is>
           <t>表E 双轨对照（page3 体检结果 ↔ 本页市民反映）</t>
         </is>
@@ -5520,7 +5542,8 @@
           <t>市民反映（本页）</t>
         </is>
       </c>
-      <c r="D43" s="33" t="inlineStr">
+      <c r="D43" s="33" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -5537,10 +5560,12 @@
           <t>燃气 6 栋 + 管线 186 栋</t>
         </is>
       </c>
-      <c r="C44" s="34" t="n">
-        <v>1102</v>
-      </c>
-      <c r="D44" s="38" t="n"/>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>1,102 条</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="inlineStr"/>
       <c r="E44" s="34" t="inlineStr">
         <is>
           <t>✓ 双证聚焦</t>
@@ -5558,10 +5583,12 @@
           <t>楼道隐患 240 栋</t>
         </is>
       </c>
-      <c r="C45" s="34" t="n">
-        <v>198</v>
-      </c>
-      <c r="D45" s="38" t="n"/>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>198 条</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="inlineStr"/>
       <c r="E45" s="34" t="inlineStr">
         <is>
           <t>✓ 双证聚焦</t>
@@ -5579,10 +5606,12 @@
           <t>结构 42 + 围护 454（堡坎）</t>
         </is>
       </c>
-      <c r="C46" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="D46" s="38" t="n"/>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>18 条</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="inlineStr"/>
       <c r="E46" s="34" t="inlineStr">
         <is>
           <t>◐ 体检独证</t>
@@ -5600,73 +5629,76 @@
           <t>（体检无对应）</t>
         </is>
       </c>
-      <c r="C47" s="34" t="n">
-        <v>723</v>
-      </c>
-      <c r="D47" s="38" t="n"/>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>723 条</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="inlineStr"/>
       <c r="E47" s="34" t="inlineStr">
         <is>
           <t>◑ 市民独证</t>
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49" ht="20" customHeight="1" s="11">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="A49" s="44" t="inlineStr">
         <is>
           <t>表F 口径详注</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1" s="11">
-      <c r="A50" s="37" t="inlineStr">
+      <c r="A50" s="44" t="inlineStr">
         <is>
           <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1" s="11">
-      <c r="A51" s="37" t="inlineStr">
-        <is>
-          <t>② 命中体检对象 = 西陵区+伍家岗区（12345_西陵+伍家岗.geojson）；区级点（区质心）视作精准合并；分级 = 精确社区 / 精确村 / 区级+范围外（非社区村面）</t>
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>② 命中体检对象 = 西陵区+伍家岗区；区级点视作精准合并；社区/村 sjoin 由 bbox 改精确点在面内（修复 3,840 错标）；分级 = 精确社区 / 精确村 / 区级+范围外</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1" s="11">
-      <c r="A52" s="37" t="inlineStr">
+      <c r="A52" s="44" t="inlineStr">
         <is>
           <t>③ 社区与村分别统计，不混淆</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="11">
-      <c r="A53" s="37" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>④ 全量（投诉+求助）5,005 = 命中西陵+伍家 2,041 + 范围外（点军/猇亭/夷陵）616 + 无坐标 2,348</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="11">
-      <c r="A54" s="37" t="inlineStr">
-        <is>
-          <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v4·命中西陵+伍家）· 制作：Codex · 2026-08-13</t>
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v5·命中西陵+伍家·sjoin 精确）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A51:I51"/>
     <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A51:I51"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A30:I30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7977,16 +8009,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="11">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>民生基础需求 · 市民反映（page6）</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1" s="11">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>表A 5 类问题明细（命中体检对象·西陵+伍家岗·区级合并）</t>
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>表A 5 类问题明细（命中体检对象·西陵+伍家岗·区级合并·社区 sjoin 精确）</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8070,7 @@
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
@@ -8046,7 +8079,7 @@
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>港务、汕头路、宝联、八一路、伍临路</t>
+          <t>朝阳路、万达、建设、港务、岳湾路</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8098,7 @@
         </is>
       </c>
       <c r="D6" s="35" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
@@ -8074,7 +8107,7 @@
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>港务、宝联、八一路、张家湾、汕头路</t>
+          <t>万达、朝阳路、港务、张家湾、岳湾路</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8126,7 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
@@ -8102,7 +8135,7 @@
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>港务、汕头路、伍临路、魏家湾、东星</t>
+          <t>朝阳路、建设、港务、万达、伍临路</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8163,7 @@
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>港务、东站路、汕头路、花艳、宝联</t>
+          <t>万达、朝阳路、花艳、张家湾、大学路</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8182,7 @@
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
@@ -8158,12 +8191,13 @@
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>港务、汕头路、宝联、东星、张家湾</t>
-        </is>
-      </c>
-    </row>
+          <t>港务、朝阳路、万达、伍临路、建设</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1" s="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>表B 规模总表（命中体检对象·区级视作精准合并）</t>
         </is>
@@ -8208,13 +8242,13 @@
         </is>
       </c>
       <c r="B13" s="35" t="n">
-        <v>2502</v>
+        <v>1919</v>
       </c>
       <c r="C13" s="35" t="n">
-        <v>54</v>
+        <v>615</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>1133</v>
+        <v>1155</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>3689</v>
@@ -8232,13 +8266,13 @@
         </is>
       </c>
       <c r="B14" s="35" t="n">
-        <v>1143</v>
+        <v>812</v>
       </c>
       <c r="C14" s="35" t="n">
-        <v>15</v>
+        <v>334</v>
       </c>
       <c r="D14" s="35" t="n">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="E14" s="35" t="n">
         <v>1870</v>
@@ -8256,13 +8290,13 @@
         </is>
       </c>
       <c r="B15" s="35" t="n">
-        <v>1688</v>
+        <v>1404</v>
       </c>
       <c r="C15" s="35" t="n">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>758</v>
+        <v>774</v>
       </c>
       <c r="E15" s="35" t="n">
         <v>2466</v>
@@ -8280,13 +8314,13 @@
         </is>
       </c>
       <c r="B16" s="35" t="n">
-        <v>730</v>
+        <v>550</v>
       </c>
       <c r="C16" s="35" t="n">
-        <v>28</v>
+        <v>203</v>
       </c>
       <c r="D16" s="35" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E16" s="35" t="n">
         <v>1027</v>
@@ -8304,13 +8338,13 @@
         </is>
       </c>
       <c r="B17" s="35" t="n">
-        <v>1351</v>
+        <v>1032</v>
       </c>
       <c r="C17" s="35" t="n">
-        <v>35</v>
+        <v>349</v>
       </c>
       <c r="D17" s="35" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E17" s="35" t="n">
         <v>2296</v>
@@ -8328,13 +8362,13 @@
         </is>
       </c>
       <c r="B18" s="33" t="n">
-        <v>7414</v>
+        <v>5717</v>
       </c>
       <c r="C18" s="33" t="n">
-        <v>152</v>
+        <v>1789</v>
       </c>
       <c r="D18" s="33" t="n">
-        <v>3782</v>
+        <v>3842</v>
       </c>
       <c r="E18" s="33" t="n">
         <v>11348</v>
@@ -8346,16 +8380,16 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="11">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>口径链：全量（投诉+求助）43,118 → 有坐标 15,469 → 命中西陵+伍家 11,348（精确社区 7,414 + 村 152 + 区级 3,697 合并 + 范围外 85）· 范围外（点军/猇亭/夷陵）4,121 · 无坐标 27,649</t>
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>口径链：全量（投诉+求助）43,118 → 有坐标 15,469 → 命中西陵+伍家 11,348（精确社区 5,717 + 村 1,789 + 区级 3,697 合并 + 范围外 145）· 范围外（点军/猇亭/夷陵）4,121 · 无坐标 27,649</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" s="11">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>表C 社区 TOP10（ok 点·社区口径）</t>
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>表C 社区 TOP10（精确点·社区口径·占精确社区 5,717）</t>
         </is>
       </c>
     </row>
@@ -8392,22 +8426,20 @@
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>港务社区</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
+          <t>朝阳路社区</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n">
+        <v>536</v>
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
         <is>
-          <t>噪声 360、住宅 225、物业 181、停车 144</t>
+          <t>噪声 189、住宅 158、物业 87</t>
         </is>
       </c>
     </row>
@@ -8417,22 +8449,20 @@
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>汕头路社区</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
+          <t>万达社区</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="n">
+        <v>451</v>
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>住宅 208、噪声 193、物业 90</t>
+          <t>噪声 170、停车 83、住宅 76</t>
         </is>
       </c>
     </row>
@@ -8442,22 +8472,20 @@
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>宝联社区</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
+          <t>港务社区</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n">
+        <v>334</v>
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>噪声 158、停车 78、物业 72</t>
+          <t>噪声 103、物业 93、住宅 79</t>
         </is>
       </c>
     </row>
@@ -8467,22 +8495,20 @@
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>八一路社区</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
+          <t>建设社区</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="n">
+        <v>320</v>
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>噪声 142、停车 72</t>
+          <t>噪声 150、住宅 89、物业 38</t>
         </is>
       </c>
     </row>
@@ -8492,22 +8518,20 @@
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>东星社区</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>岳湾路社区</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="n">
+        <v>206</v>
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>住宅 73、物业 70</t>
+          <t>噪声 89、停车 38、住宅 35</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8541,20 @@
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>张家湾社区</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
+          <t>伍临路社区</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="n">
+        <v>200</v>
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>物业 65、停车 62</t>
+          <t>住宅 70、噪声 66、物业 42</t>
         </is>
       </c>
     </row>
@@ -8542,22 +8564,20 @@
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>伍临路社区</t>
-        </is>
-      </c>
-      <c r="C28" s="35" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+          <t>大学路社区</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="n">
+        <v>178</v>
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>噪声 109、住宅 76</t>
+          <t>噪声 72、住宅 30、物业 29</t>
         </is>
       </c>
     </row>
@@ -8567,22 +8587,20 @@
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>魏家湾社区</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
+          <t>张家湾社区</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="n">
+        <v>159</v>
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>住宅 74</t>
+          <t>噪声 46、停车 41、物业 35</t>
         </is>
       </c>
     </row>
@@ -8592,22 +8610,20 @@
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>艾家嘴社区</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
+          <t>宝联社区</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="n">
+        <v>127</v>
       </c>
       <c r="D30" s="35" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>噪声 43、停车 31、住宅 23</t>
         </is>
       </c>
     </row>
@@ -8617,208 +8633,234 @@
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>东站路社区</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
+          <t>枫香树社区</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="n">
+        <v>115</v>
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
         <is>
-          <t>出行 62</t>
+          <t>住宅 39、噪声 23、停车 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>表D 行政村诉求排行（精确点·村口径·top10）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" s="11">
       <c r="A33" s="32" t="inlineStr">
         <is>
-          <t>表D 行政村诉求排行（精确点·村口径）</t>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>诉求数</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>占比</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" s="11">
-      <c r="A34" s="33" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
+      <c r="A34" s="33" t="n">
+        <v>1</v>
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>村</t>
-        </is>
-      </c>
-      <c r="C34" s="33" t="inlineStr">
-        <is>
-          <t>诉求数</t>
-        </is>
+          <t>共勤村</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>470</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" s="11">
       <c r="A35" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>火光村</t>
+          <t>旭光村</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>89</v>
+        <v>321</v>
       </c>
       <c r="D35" s="35" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" s="11">
       <c r="A36" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>旭光村</t>
+          <t>汉宜村</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="D36" s="35" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" s="11">
       <c r="A37" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>联丰村</t>
+          <t>火光村</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="D37" s="35" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" s="11">
       <c r="A38" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>共联村</t>
+          <t>共和村</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="D38" s="35" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" s="11">
       <c r="A39" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>共勤村</t>
+          <t>合益村</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" s="11">
       <c r="A40" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>共谊村</t>
+          <t>共联村</t>
         </is>
       </c>
       <c r="C40" s="35" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" s="11">
       <c r="A41" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>灵宝村</t>
+          <t>共同村</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" s="11">
       <c r="A42" s="35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>灵宝村</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>联丰村</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="n">
+        <v>37</v>
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="n"/>
-      <c r="B43" s="42" t="n"/>
-      <c r="C43" s="41" t="n"/>
-      <c r="D43" s="41" t="n"/>
+      <c r="A43" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>共前村</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="D43" s="41" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1" s="11">
-      <c r="A44" s="32" t="inlineStr">
+      <c r="A44" s="44" t="inlineStr">
         <is>
           <t>表E 双轨对照（page5 体检结果 ↔ 本页市民反映）</t>
         </is>
@@ -8840,7 +8882,8 @@
           <t>市民反映（本页）</t>
         </is>
       </c>
-      <c r="D45" s="33" t="inlineStr">
+      <c r="D45" s="33" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -8857,10 +8900,12 @@
           <t>泊位 140 处/充电桩 84/电动车 50</t>
         </is>
       </c>
-      <c r="C46" s="34" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D46" s="38" t="n"/>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>1,870 条</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="inlineStr"/>
       <c r="E46" s="34" t="inlineStr">
         <is>
           <t>✓ 双证聚焦</t>
@@ -8878,10 +8923,12 @@
           <t>非成套 31/适老化 39</t>
         </is>
       </c>
-      <c r="C47" s="34" t="n">
-        <v>2466</v>
-      </c>
-      <c r="D47" s="38" t="n"/>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>2,466 条</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="inlineStr"/>
       <c r="E47" s="34" t="inlineStr">
         <is>
           <t>✓ 双证聚焦</t>
@@ -8899,10 +8946,12 @@
           <t>未物业 273 个/乱停放 5</t>
         </is>
       </c>
-      <c r="C48" s="34" t="n">
-        <v>2296</v>
-      </c>
-      <c r="D48" s="38" t="n"/>
+      <c r="C48" s="34" t="inlineStr">
+        <is>
+          <t>2,296 条</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="inlineStr"/>
       <c r="E48" s="34" t="inlineStr">
         <is>
           <t>✓ 双证聚焦</t>
@@ -8920,10 +8969,12 @@
           <t>步行道 2.09 千米</t>
         </is>
       </c>
-      <c r="C49" s="34" t="n">
-        <v>1027</v>
-      </c>
-      <c r="D49" s="38" t="n"/>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>1,027 条</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="inlineStr"/>
       <c r="E49" s="34" t="inlineStr">
         <is>
           <t>✓ 相关印证</t>
@@ -8941,55 +8992,58 @@
           <t>（体检无对应）</t>
         </is>
       </c>
-      <c r="C50" s="34" t="n">
-        <v>3689</v>
-      </c>
-      <c r="D50" s="38" t="n"/>
+      <c r="C50" s="34" t="inlineStr">
+        <is>
+          <t>3,689 条</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="inlineStr"/>
       <c r="E50" s="34" t="inlineStr">
         <is>
           <t>◑ 市民独证</t>
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="20" customHeight="1" s="11">
-      <c r="A52" s="32" t="inlineStr">
+      <c r="A52" s="44" t="inlineStr">
         <is>
           <t>表F 口径详注</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1" s="11">
-      <c r="A53" s="37" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1" s="11">
-      <c r="A54" s="37" t="inlineStr">
-        <is>
-          <t>② 命中体检对象 = 西陵区+伍家岗区（12345_西陵+伍家岗.geojson）；区级点（区质心）视作精准合并；分级 = 精确社区 / 精确村 / 区级+范围外（非社区村面）</t>
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>② 命中体检对象 = 西陵区+伍家岗区；区级点视作精准合并；社区/村 sjoin 由 bbox 改精确点在面内（修复 3,840 错标）；分级 = 精确社区 / 精确村 / 区级+范围外</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1" s="11">
-      <c r="A55" s="37" t="inlineStr">
+      <c r="A55" s="44" t="inlineStr">
         <is>
           <t>③ 社区与村分别统计，不混淆</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1" s="11">
-      <c r="A56" s="37" t="inlineStr">
+      <c r="A56" s="44" t="inlineStr">
         <is>
           <t>④ 全量（投诉+求助）43,118 = 命中西陵+伍家 11,348 + 范围外（点军/猇亭/夷陵）4,121 + 无坐标 27,649</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1" s="11">
-      <c r="A57" s="37" t="inlineStr">
-        <is>
-          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v4·命中西陵+伍家）· 制作：Codex · 2026-08-13</t>
+      <c r="A57" s="44" t="inlineStr">
+        <is>
+          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v5·命中西陵+伍家·sjoin 精确）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8999,7 +9053,7 @@
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A56:I56"/>

--- a/DATA/analysis/图数表出图_PPT表格汇总.xlsx
+++ b/DATA/analysis/图数表出图_PPT表格汇总.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -103,6 +103,9 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -112,7 +115,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -282,11 +285,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -414,6 +461,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4699,16 +4758,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1" s="18">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>安全韧性问题 · 市民反映（page4）</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20.1" customHeight="1" s="18">
-      <c r="A3" s="47" t="inlineStr">
-        <is>
-          <t>表A 4 类问题明细（命中体检对象·西陵+伍家岗·区级合并·社区 sjoin 精确）</t>
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>表A 4 类问题明细（命中体检对象·西陵+伍家岗·区级按口径计入·去村）</t>
         </is>
       </c>
     </row>
@@ -4751,11 +4811,11 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>1102</v>
+        <v>967</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -4779,11 +4839,11 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>723</v>
+        <v>618</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
@@ -4807,11 +4867,11 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -4835,11 +4895,11 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
@@ -4856,10 +4916,11 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="20.1" customHeight="1" s="18">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>表B 规模总表（命中体检对象·区级视作精准合并）</t>
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>表B 规模总表（命中体检对象·区级按口径计入·去村）</t>
         </is>
       </c>
     </row>
@@ -4876,24 +4937,20 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>精确村</t>
+          <t>区级+范围外（合并）</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>区级+范围外（合并）</t>
+          <t>命中合计</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>命中合计</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
           <t>占比</t>
         </is>
       </c>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" s="18">
       <c r="A12" s="11" t="inlineStr">
@@ -4905,19 +4962,17 @@
         <v>538</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>135</v>
+        <v>429</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>429</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>1102</v>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>54.0%</t>
-        </is>
-      </c>
+        <v>967</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" s="18">
       <c r="A13" s="11" t="inlineStr">
@@ -4929,19 +4984,17 @@
         <v>371</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>247</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>723</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>35.4%</t>
-        </is>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>35.2%</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" s="18">
       <c r="A14" s="11" t="inlineStr">
@@ -4953,19 +5006,17 @@
         <v>119</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>198</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>9.7%</t>
-        </is>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" s="18">
       <c r="A15" s="11" t="inlineStr">
@@ -4977,19 +5028,17 @@
         <v>7</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" s="18">
       <c r="A16" s="13" t="inlineStr">
@@ -5001,29 +5050,27 @@
         <v>1035</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>284</v>
+        <v>722</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>722</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>2041</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+        <v>1757</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1" s="18">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>口径链：全量（投诉+求助）5,005 → 有坐标 2,657 → 命中西陵+伍家 2,041（精确社区 1,035 + 村 284 + 区级 691 合并 + 范围外 31）· 范围外（点军/猇亭/夷陵）616 · 无坐标 2,348</t>
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>口径链：命中体检对象（西陵+伍家岗·去村）1,757 = 精确社区 1,035 + 区级 691 + 范围外 31</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20.1" customHeight="1" s="18">
-      <c r="A18" s="47" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>表C 社区 TOP10（精确点·社区口径·占精确社区 1,035）</t>
         </is>
@@ -5287,393 +5334,269 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="48" t="inlineStr">
-        <is>
-          <t>表D 行政村诉求排行（精确点·村口径·top10）</t>
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>表D 双轨对照（page3 体检结果 ↔ 本页市民反映）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20.1" customHeight="1" s="18">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>主题</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>村</t>
+          <t>体检发现（page3）</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>诉求数</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>占比</t>
+          <t>市民反映（本页）</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>判定</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21.95" customHeight="1" s="18">
-      <c r="A32" s="10" t="n">
-        <v>1</v>
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>管网安全</t>
+        </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>汉宜村</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>86</v>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>30.3%</t>
+          <t>燃气 6 栋 + 管线 186 栋</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>967 条</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21.95" customHeight="1" s="18">
-      <c r="A33" s="12" t="n">
-        <v>2</v>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>消防安全</t>
+        </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>旭光村</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>14.4%</t>
+          <t>楼道隐患 240 栋</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>159 条</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21.95" customHeight="1" s="18">
-      <c r="A34" s="12" t="n">
-        <v>3</v>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>环境安全</t>
+        </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>共勤村</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>14.1%</t>
+          <t>结构 42 + 围护 454（堡坎）</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>13 条</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>◐ 体检独证</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21.95" customHeight="1" s="18">
-      <c r="A35" s="12" t="n">
-        <v>4</v>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>出行安全</t>
+        </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>共和村</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>11.3%</t>
+          <t>（体检无对应）</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>618 条</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>◑ 市民独证</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21.95" customHeight="1" s="18">
-      <c r="A36" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>火光村</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>8.5%</t>
-        </is>
-      </c>
+      <c r="A36" s="12" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
     </row>
     <row r="37" ht="21.95" customHeight="1" s="18">
-      <c r="A37" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>共联村</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
+      <c r="A37" s="52" t="inlineStr">
+        <is>
+          <t>表E 口径详注</t>
+        </is>
+      </c>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="53" t="n"/>
+      <c r="G37" s="53" t="n"/>
+      <c r="H37" s="53" t="n"/>
+      <c r="I37" s="54" t="n"/>
     </row>
     <row r="38" ht="21.95" customHeight="1" s="18">
-      <c r="A38" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>合益村</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
+      <c r="A38" s="52" t="inlineStr">
+        <is>
+          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
+        </is>
+      </c>
+      <c r="B38" s="53" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
+      <c r="E38" s="53" t="n"/>
+      <c r="F38" s="53" t="n"/>
+      <c r="G38" s="53" t="n"/>
+      <c r="H38" s="53" t="n"/>
+      <c r="I38" s="54" t="n"/>
     </row>
     <row r="39" ht="21.95" customHeight="1" s="18">
-      <c r="A39" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>共谊村</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+      <c r="A39" s="52" t="inlineStr">
+        <is>
+          <t>② 命中体检对象 = 西陵区+伍家岗区；去村（村点不计入）；区级点按区级口径计入、不参与社区精确归集；社区 sjoin 精确点在面内（修复 3,840 错标）</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
+      <c r="E39" s="53" t="n"/>
+      <c r="F39" s="53" t="n"/>
+      <c r="G39" s="53" t="n"/>
+      <c r="H39" s="53" t="n"/>
+      <c r="I39" s="54" t="n"/>
     </row>
     <row r="40" ht="21.95" customHeight="1" s="18">
-      <c r="A40" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>联丰村</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
+      <c r="A40" s="52" t="inlineStr">
+        <is>
+          <t>③ 图斑 1,757 = 精确社区 1,035 + 区级 691 + 范围外 31（已去村）</t>
+        </is>
+      </c>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
+      <c r="I40" s="54" t="n"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="18">
-      <c r="A41" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>共前村</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>1.8%</t>
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>数据源：DATA/analysis/汇总/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v6·去村）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20.1" customHeight="1" s="18">
-      <c r="A42" s="47" t="inlineStr">
-        <is>
-          <t>表E 双轨对照（page3 体检结果 ↔ 本页市民反映）</t>
-        </is>
-      </c>
+      <c r="A42" s="47" t="n"/>
     </row>
     <row r="43" ht="21.95" customHeight="1" s="18">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>主题</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>体检发现（page3）</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>市民反映（本页）</t>
-        </is>
-      </c>
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
       <c r="D43" s="10" t="n"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
     </row>
     <row r="44" ht="26.1" customHeight="1" s="18">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>管网安全</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>燃气 6 栋 + 管线 186 栋</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>1,102 条</t>
-        </is>
-      </c>
+      <c r="A44" s="12" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
       <c r="D44" s="14" t="n"/>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
+      <c r="E44" s="11" t="n"/>
     </row>
     <row r="45" ht="26.1" customHeight="1" s="18">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>消防安全</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>楼道隐患 240 栋</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>198 条</t>
-        </is>
-      </c>
+      <c r="A45" s="12" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
       <c r="D45" s="14" t="n"/>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
+      <c r="E45" s="11" t="n"/>
     </row>
     <row r="46" ht="26.1" customHeight="1" s="18">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>环境安全</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>结构 42 + 围护 454（堡坎）</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>18 条</t>
-        </is>
-      </c>
+      <c r="A46" s="12" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
       <c r="D46" s="14" t="n"/>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>◐ 体检独证</t>
-        </is>
-      </c>
+      <c r="E46" s="11" t="n"/>
     </row>
     <row r="47" ht="26.1" customHeight="1" s="18">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>出行安全</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>（体检无对应）</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>723 条</t>
-        </is>
-      </c>
+      <c r="A47" s="12" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
       <c r="D47" s="14" t="n"/>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>◑ 市民独证</t>
-        </is>
-      </c>
-    </row>
+      <c r="E47" s="11" t="n"/>
+    </row>
+    <row r="48"/>
     <row r="49" ht="20.1" customHeight="1" s="18">
-      <c r="A49" s="47" t="inlineStr">
-        <is>
-          <t>表F 口径详注</t>
-        </is>
-      </c>
+      <c r="A49" s="47" t="n"/>
     </row>
     <row r="50" ht="15.95" customHeight="1" s="18">
-      <c r="A50" s="47" t="inlineStr">
-        <is>
-          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
-        </is>
-      </c>
+      <c r="A50" s="47" t="n"/>
     </row>
     <row r="51" ht="15.95" customHeight="1" s="18">
-      <c r="A51" s="47" t="inlineStr">
-        <is>
-          <t>② 命中体检对象 = 西陵区+伍家岗区；区级点视作精准合并；社区/村 sjoin 由 bbox 改精确点在面内（修复 3,840 错标）；分级 = 精确社区 / 精确村 / 区级+范围外</t>
-        </is>
-      </c>
+      <c r="A51" s="47" t="n"/>
     </row>
     <row r="52" ht="15.95" customHeight="1" s="18">
-      <c r="A52" s="47" t="inlineStr">
-        <is>
-          <t>③ 社区与村分别统计，不混淆</t>
-        </is>
-      </c>
+      <c r="A52" s="47" t="n"/>
     </row>
     <row r="53" ht="15.95" customHeight="1" s="18">
-      <c r="A53" s="47" t="inlineStr">
-        <is>
-          <t>④ 全量（投诉+求助）5,005 = 命中西陵+伍家 2,041 + 范围外（点军/猇亭/夷陵）616 + 无坐标 2,348</t>
-        </is>
-      </c>
+      <c r="A53" s="47" t="n"/>
     </row>
     <row r="54" ht="15.95" customHeight="1" s="18">
-      <c r="A54" s="47" t="inlineStr">
-        <is>
-          <t>数据源：DATA/analysis/page4_安全韧性_市民反映_分析汇总_2026-08-13.md（v5·命中西陵+伍家·sjoin 精确）· 制作：Codex · 2026-08-13</t>
-        </is>
-      </c>
+      <c r="A54" s="47" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A51:I51"/>
+  <mergeCells count="11">
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -7983,16 +7906,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1" s="18">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>民生基础需求 · 市民反映（page6）</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20.1" customHeight="1" s="18">
-      <c r="A3" s="47" t="inlineStr">
-        <is>
-          <t>表A 5 类问题明细（命中体检对象·西陵+伍家岗·区级合并·社区 sjoin 精确）</t>
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>表A 5 类问题明细（命中体检对象·西陵+伍家岗·区级按口径计入·去村）</t>
         </is>
       </c>
     </row>
@@ -8035,11 +7959,11 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>3689</v>
+        <v>3074</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -8063,11 +7987,11 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1870</v>
+        <v>1536</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
@@ -8091,11 +8015,11 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>2466</v>
+        <v>2178</v>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -8119,11 +8043,11 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1027</v>
+        <v>824</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
@@ -8147,11 +8071,11 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2296</v>
+        <v>1947</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
@@ -8168,10 +8092,11 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="20.1" customHeight="1" s="18">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>表B 规模总表（命中体检对象·区级视作精准合并）</t>
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>表B 规模总表（命中体检对象·区级按口径计入·去村）</t>
         </is>
       </c>
     </row>
@@ -8188,24 +8113,20 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>精确村</t>
+          <t>区级+范围外（合并）</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>区级+范围外（合并）</t>
+          <t>命中合计</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>命中合计</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
           <t>占比</t>
         </is>
       </c>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" s="18">
       <c r="A13" s="11" t="inlineStr">
@@ -8217,19 +8138,17 @@
         <v>1919</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>615</v>
+        <v>1155</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>1155</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>3689</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>32.5%</t>
-        </is>
-      </c>
+        <v>3074</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>32.2%</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" s="18">
       <c r="A14" s="11" t="inlineStr">
@@ -8241,19 +8160,17 @@
         <v>812</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>334</v>
+        <v>724</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>724</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>1870</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>16.5%</t>
-        </is>
-      </c>
+        <v>1536</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" s="18">
       <c r="A15" s="11" t="inlineStr">
@@ -8265,19 +8182,17 @@
         <v>1404</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>288</v>
+        <v>774</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>774</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>2466</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>21.7%</t>
-        </is>
-      </c>
+        <v>2178</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>22.8%</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" s="18">
       <c r="A16" s="11" t="inlineStr">
@@ -8289,19 +8204,17 @@
         <v>550</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>203</v>
+        <v>274</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>274</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>1027</v>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>9.1%</t>
-        </is>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>8.6%</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" s="18">
       <c r="A17" s="11" t="inlineStr">
@@ -8313,19 +8226,17 @@
         <v>1032</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>349</v>
+        <v>915</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>915</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>2296</v>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
+        <v>1947</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n"/>
     </row>
     <row r="18" ht="21.95" customHeight="1" s="18">
       <c r="A18" s="13" t="inlineStr">
@@ -8337,29 +8248,27 @@
         <v>5717</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1789</v>
+        <v>3842</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3842</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>11348</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+        <v>9559</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
+      <c r="F18" s="10" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="18">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t>口径链：全量（投诉+求助）43,118 → 有坐标 15,469 → 命中西陵+伍家 11,348（精确社区 5,717 + 村 1,789 + 区级 3,697 合并 + 范围外 145）· 范围外（点军/猇亭/夷陵）4,121 · 无坐标 27,649</t>
+      <c r="A19" s="50" t="inlineStr">
+        <is>
+          <t>口径链：命中体检对象（西陵+伍家岗·去村）9,559 = 精确社区 5,717 + 区级 3,697 + 范围外 145</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="18">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>表C 社区 TOP10（精确点·社区口径·占精确社区 5,717）</t>
         </is>
@@ -8623,416 +8532,288 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
-        <is>
-          <t>表D 行政村诉求排行（精确点·村口径·top10）</t>
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>表D 双轨对照（page5 体检结果 ↔ 本页市民反映）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20.1" customHeight="1" s="18">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>主题</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>村</t>
+          <t>体检发现（page5）</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>诉求数</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>占比</t>
+          <t>市民反映（本页）</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>判定</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21.95" customHeight="1" s="18">
-      <c r="A34" s="10" t="n">
-        <v>1</v>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>停车</t>
+        </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>共勤村</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>470</v>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>26.3%</t>
+          <t>泊位 140 处/充电桩 84/电动车 50</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>1,536 条</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21.95" customHeight="1" s="18">
-      <c r="A35" s="12" t="n">
-        <v>2</v>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>旭光村</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>321</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>17.9%</t>
+          <t>非成套 31/适老化 39</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>2,178 条</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21.95" customHeight="1" s="18">
-      <c r="A36" s="12" t="n">
-        <v>3</v>
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>物业</t>
+        </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>汉宜村</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n">
-        <v>279</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>15.6%</t>
+          <t>未物业 273 个/乱停放 5</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>1,947 条</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>✓ 双证聚焦</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21.95" customHeight="1" s="18">
-      <c r="A37" s="12" t="n">
-        <v>4</v>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>出行</t>
+        </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>火光村</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="n">
-        <v>221</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>12.4%</t>
+          <t>步行道 2.09 千米</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>824 条</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>✓ 相关印证</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21.95" customHeight="1" s="18">
-      <c r="A38" s="12" t="n">
-        <v>5</v>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>噪声</t>
+        </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>共和村</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>158</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>8.8%</t>
+          <t>（体检无对应）</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>3,074 条</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>◑ 市民独证</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21.95" customHeight="1" s="18">
-      <c r="A39" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>合益村</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>125</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>7.0%</t>
-        </is>
-      </c>
+      <c r="A39" s="12" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
     </row>
     <row r="40" ht="21.95" customHeight="1" s="18">
-      <c r="A40" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>共联村</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
+      <c r="A40" s="52" t="inlineStr">
+        <is>
+          <t>表E 口径详注</t>
+        </is>
+      </c>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
+      <c r="I40" s="54" t="n"/>
     </row>
     <row r="41" ht="21.95" customHeight="1" s="18">
-      <c r="A41" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>共同村</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="A41" s="52" t="inlineStr">
+        <is>
+          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
+        </is>
+      </c>
+      <c r="B41" s="53" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
+      <c r="E41" s="53" t="n"/>
+      <c r="F41" s="53" t="n"/>
+      <c r="G41" s="53" t="n"/>
+      <c r="H41" s="53" t="n"/>
+      <c r="I41" s="54" t="n"/>
     </row>
     <row r="42" ht="21.95" customHeight="1" s="18">
-      <c r="A42" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>联丰村</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+      <c r="A42" s="52" t="inlineStr">
+        <is>
+          <t>② 命中体检对象 = 西陵区+伍家岗区；去村（村点不计入）；区级点按区级口径计入、不参与社区精确归集；社区 sjoin 精确点在面内（修复 3,840 错标）</t>
+        </is>
+      </c>
+      <c r="B42" s="53" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
+      <c r="E42" s="53" t="n"/>
+      <c r="F42" s="53" t="n"/>
+      <c r="G42" s="53" t="n"/>
+      <c r="H42" s="53" t="n"/>
+      <c r="I42" s="54" t="n"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="18">
-      <c r="A43" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>共前村</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>1.6%</t>
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>③ 图斑 9,559 = 精确社区 5,717 + 区级 3,697 + 范围外 145（已去村）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20.1" customHeight="1" s="18">
-      <c r="A44" s="47" t="inlineStr">
-        <is>
-          <t>表E 双轨对照（page5 体检结果 ↔ 本页市民反映）</t>
+      <c r="A44" s="50" t="inlineStr">
+        <is>
+          <t>数据源：DATA/analysis/汇总/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v6·去村）· 制作：Codex · 2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21.95" customHeight="1" s="18">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>主题</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>体检发现（page5）</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>市民反映（本页）</t>
-        </is>
-      </c>
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
       <c r="D45" s="10" t="n"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="26.1" customHeight="1" s="18">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>停车</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>泊位 140 处/充电桩 84/电动车 50</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>1,870 条</t>
-        </is>
-      </c>
+      <c r="A46" s="12" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
       <c r="D46" s="14" t="n"/>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
+      <c r="E46" s="11" t="n"/>
     </row>
     <row r="47" ht="26.1" customHeight="1" s="18">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>住宅</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>非成套 31/适老化 39</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>2,466 条</t>
-        </is>
-      </c>
+      <c r="A47" s="12" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
       <c r="D47" s="14" t="n"/>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
+      <c r="E47" s="11" t="n"/>
     </row>
     <row r="48" ht="26.1" customHeight="1" s="18">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>物业</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>未物业 273 个/乱停放 5</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>2,296 条</t>
-        </is>
-      </c>
+      <c r="A48" s="12" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
       <c r="D48" s="14" t="n"/>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>✓ 双证聚焦</t>
-        </is>
-      </c>
+      <c r="E48" s="11" t="n"/>
     </row>
     <row r="49" ht="26.1" customHeight="1" s="18">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>出行</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>步行道 2.09 千米</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>1,027 条</t>
-        </is>
-      </c>
+      <c r="A49" s="12" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
       <c r="D49" s="14" t="n"/>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>✓ 相关印证</t>
-        </is>
-      </c>
+      <c r="E49" s="11" t="n"/>
     </row>
     <row r="50" ht="26.1" customHeight="1" s="18">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>噪声</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>（体检无对应）</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>3,689 条</t>
-        </is>
-      </c>
+      <c r="A50" s="12" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
       <c r="D50" s="14" t="n"/>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>◑ 市民独证</t>
-        </is>
-      </c>
-    </row>
+      <c r="E50" s="11" t="n"/>
+    </row>
+    <row r="51"/>
     <row r="52" ht="20.1" customHeight="1" s="18">
-      <c r="A52" s="47" t="inlineStr">
-        <is>
-          <t>表F 口径详注</t>
-        </is>
-      </c>
+      <c r="A52" s="47" t="n"/>
     </row>
     <row r="53" ht="15.95" customHeight="1" s="18">
-      <c r="A53" s="47" t="inlineStr">
-        <is>
-          <t>① 数据源 = 12345_治理清洗版（board 直切）+ checkup 图层（坐标）治理产出（CB-30）</t>
-        </is>
-      </c>
+      <c r="A53" s="47" t="n"/>
     </row>
     <row r="54" ht="15.95" customHeight="1" s="18">
-      <c r="A54" s="47" t="inlineStr">
-        <is>
-          <t>② 命中体检对象 = 西陵区+伍家岗区；区级点视作精准合并；社区/村 sjoin 由 bbox 改精确点在面内（修复 3,840 错标）；分级 = 精确社区 / 精确村 / 区级+范围外</t>
-        </is>
-      </c>
+      <c r="A54" s="47" t="n"/>
     </row>
     <row r="55" ht="15.95" customHeight="1" s="18">
-      <c r="A55" s="47" t="inlineStr">
-        <is>
-          <t>③ 社区与村分别统计，不混淆</t>
-        </is>
-      </c>
+      <c r="A55" s="47" t="n"/>
     </row>
     <row r="56" ht="15.95" customHeight="1" s="18">
-      <c r="A56" s="47" t="inlineStr">
-        <is>
-          <t>④ 全量（投诉+求助）43,118 = 命中西陵+伍家 11,348 + 范围外（点军/猇亭/夷陵）4,121 + 无坐标 27,649</t>
-        </is>
-      </c>
+      <c r="A56" s="47" t="n"/>
     </row>
     <row r="57" ht="15.95" customHeight="1" s="18">
-      <c r="A57" s="47" t="inlineStr">
-        <is>
-          <t>数据源：DATA/analysis/page6_民生基础_市民反映_分析汇总_2026-08-13.md（v5·命中西陵+伍家·sjoin 精确）· 制作：Codex · 2026-08-13</t>
-        </is>
-      </c>
+      <c r="A57" s="47" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A57:I57"/>
+  <mergeCells count="11">
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
